--- a/data/status_saida/operacional/status_out_2026.xlsx
+++ b/data/status_saida/operacional/status_out_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opera\Desktop\app\dashboard_operacao\data\status_saida\operacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8D690FD-7354-45BB-A6E9-069F6BD9F48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EFB4020-6986-4C24-8FC5-A35250EFF697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E0A4FB7-BD17-45E6-919E-4EE82CB7546D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00452EF5-AB32-4BC4-BE8F-4ED0999574BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="426">
   <si>
     <t>Relatório de Pedidos  Geral</t>
   </si>
@@ -131,102 +131,159 @@
     <t>AGUARDANDO EXPEDICAO</t>
   </si>
   <si>
+    <t>60676</t>
+  </si>
+  <si>
+    <t>V M B GROFF COMERCIO ELETRONICO LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:47</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:27:27</t>
+  </si>
+  <si>
+    <t>EDNEIDE SANTOS</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:30:21</t>
+  </si>
+  <si>
+    <t>38493</t>
+  </si>
+  <si>
+    <t>26670</t>
+  </si>
+  <si>
+    <t>MERCADO LIVRE - CROSS</t>
+  </si>
+  <si>
+    <t>60675</t>
+  </si>
+  <si>
+    <t>60701</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:39</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:27:03</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:28:24</t>
+  </si>
+  <si>
+    <t>38528</t>
+  </si>
+  <si>
+    <t>26676</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - SHOPEE FLEX</t>
+  </si>
+  <si>
+    <t>200001873233408</t>
+  </si>
+  <si>
+    <t>15459</t>
+  </si>
+  <si>
+    <t>RHINO AUTOPARTS DISTRIBUIDORA E IMPORTADORA DE AUTO PEÇAS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:50:08</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:04:56</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:06:03</t>
+  </si>
+  <si>
+    <t>38507</t>
+  </si>
+  <si>
+    <t>26673</t>
+  </si>
+  <si>
+    <t>60702</t>
+  </si>
+  <si>
+    <t>60703</t>
+  </si>
+  <si>
+    <t>60689</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:49</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:05:53</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:06:51</t>
+  </si>
+  <si>
+    <t>38491</t>
+  </si>
+  <si>
+    <t>26675</t>
+  </si>
+  <si>
+    <t>TOTAL EXPRESS</t>
+  </si>
+  <si>
+    <t>60688</t>
+  </si>
+  <si>
+    <t>60686</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:48</t>
+  </si>
+  <si>
+    <t>60685</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:12:54</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:14:25</t>
+  </si>
+  <si>
+    <t>38492</t>
+  </si>
+  <si>
+    <t>26674</t>
+  </si>
+  <si>
+    <t>CORREIOS VETTORE</t>
+  </si>
+  <si>
+    <t>166546891073601</t>
+  </si>
+  <si>
+    <t>60683</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:50:50</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:53:39</t>
+  </si>
+  <si>
+    <t>38494</t>
+  </si>
+  <si>
+    <t>26671</t>
+  </si>
+  <si>
+    <t>JMS CARGO (JADLOG)</t>
+  </si>
+  <si>
     <t>60684</t>
   </si>
   <si>
-    <t>V M B GROFF COMERCIO ELETRONICO LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:48</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:12:54</t>
-  </si>
-  <si>
-    <t>EDNEIDE SANTOS</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:14:25</t>
-  </si>
-  <si>
-    <t>38492</t>
-  </si>
-  <si>
-    <t>26674</t>
-  </si>
-  <si>
-    <t>CORREIOS VETTORE</t>
-  </si>
-  <si>
-    <t>200001873233408</t>
-  </si>
-  <si>
-    <t>15459</t>
-  </si>
-  <si>
-    <t>RHINO AUTOPARTS DISTRIBUIDORA E IMPORTADORA DE AUTO PEÇAS LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:50:08</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:04:56</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:06:03</t>
-  </si>
-  <si>
-    <t>38507</t>
-  </si>
-  <si>
-    <t>26673</t>
-  </si>
-  <si>
-    <t>MERCADO LIVRE - CROSS</t>
-  </si>
-  <si>
-    <t>60675</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:47</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:27:27</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:30:21</t>
-  </si>
-  <si>
-    <t>38493</t>
-  </si>
-  <si>
-    <t>26670</t>
-  </si>
-  <si>
-    <t>60685</t>
-  </si>
-  <si>
-    <t>166546891073601</t>
-  </si>
-  <si>
-    <t>60683</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:50:50</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:53:39</t>
-  </si>
-  <si>
-    <t>38494</t>
-  </si>
-  <si>
-    <t>26671</t>
-  </si>
-  <si>
-    <t>JMS CARGO (JADLOG)</t>
-  </si>
-  <si>
     <t>166550891492101</t>
   </si>
   <si>
@@ -248,60 +305,237 @@
     <t>60677</t>
   </si>
   <si>
-    <t>60676</t>
-  </si>
-  <si>
     <t>EM SEPARACAO</t>
   </si>
   <si>
+    <t>116923</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:10</t>
+  </si>
+  <si>
+    <t>38522</t>
+  </si>
+  <si>
+    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>116930</t>
+  </si>
+  <si>
+    <t>38525</t>
+  </si>
+  <si>
+    <t>60691</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:35</t>
+  </si>
+  <si>
+    <t>38526</t>
+  </si>
+  <si>
+    <t>60692</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:36</t>
+  </si>
+  <si>
+    <t>60693</t>
+  </si>
+  <si>
+    <t>116927</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:46</t>
+  </si>
+  <si>
+    <t>38516</t>
+  </si>
+  <si>
+    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
+  </si>
+  <si>
+    <t>60694</t>
+  </si>
+  <si>
+    <t>60695</t>
+  </si>
+  <si>
+    <t>60696</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:37</t>
+  </si>
+  <si>
+    <t>38527</t>
+  </si>
+  <si>
+    <t>60697</t>
+  </si>
+  <si>
+    <t>60698</t>
+  </si>
+  <si>
+    <t>38529</t>
+  </si>
+  <si>
+    <t>60699</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:38</t>
+  </si>
+  <si>
+    <t>38530</t>
+  </si>
+  <si>
+    <t>SHOPEE EXPRESSS</t>
+  </si>
+  <si>
+    <t>60700</t>
+  </si>
+  <si>
+    <t>38531</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - ML FLEX</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:40</t>
+  </si>
+  <si>
+    <t>38532</t>
+  </si>
+  <si>
+    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
+  </si>
+  <si>
+    <t>116921</t>
+  </si>
+  <si>
+    <t>38524</t>
+  </si>
+  <si>
+    <t>60687</t>
+  </si>
+  <si>
+    <t>67852</t>
+  </si>
+  <si>
+    <t>81186213</t>
+  </si>
+  <si>
+    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:50:26</t>
+  </si>
+  <si>
+    <t>38505</t>
+  </si>
+  <si>
+    <t>VENETO</t>
+  </si>
+  <si>
+    <t>02741</t>
+  </si>
+  <si>
+    <t>81186214</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:29:45</t>
+  </si>
+  <si>
+    <t>38510</t>
+  </si>
+  <si>
+    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
+  </si>
+  <si>
+    <t>Doação JSA-Zandoná</t>
+  </si>
+  <si>
+    <t>81186217</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:02:42</t>
+  </si>
+  <si>
+    <t>38512</t>
+  </si>
+  <si>
+    <t>116916</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:53</t>
+  </si>
+  <si>
+    <t>38508</t>
+  </si>
+  <si>
+    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
+  </si>
+  <si>
+    <t>116917</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:54</t>
+  </si>
+  <si>
+    <t>38509</t>
+  </si>
+  <si>
+    <t>159976</t>
+  </si>
+  <si>
+    <t>81186218</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:20:18</t>
+  </si>
+  <si>
+    <t>38513</t>
+  </si>
+  <si>
+    <t>483962</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:22:35</t>
+  </si>
+  <si>
+    <t>38511</t>
+  </si>
+  <si>
+    <t>116924</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:45</t>
+  </si>
+  <si>
+    <t>38515</t>
+  </si>
+  <si>
     <t>116925</t>
   </si>
   <si>
-    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:45</t>
-  </si>
-  <si>
     <t>38517</t>
   </si>
   <si>
-    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
-  </si>
-  <si>
-    <t>Doação JSA-Zandoná</t>
-  </si>
-  <si>
-    <t>81186217</t>
-  </si>
-  <si>
-    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:02:42</t>
-  </si>
-  <si>
-    <t>38512</t>
-  </si>
-  <si>
-    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
-  </si>
-  <si>
     <t>116926</t>
   </si>
   <si>
     <t>38514</t>
   </si>
   <si>
-    <t>116927</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:46</t>
-  </si>
-  <si>
-    <t>38516</t>
-  </si>
-  <si>
     <t>116928</t>
   </si>
   <si>
@@ -323,136 +557,25 @@
     <t>38521</t>
   </si>
   <si>
-    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
-  </si>
-  <si>
     <t>116920</t>
   </si>
   <si>
     <t>38520</t>
   </si>
   <si>
-    <t>116921</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:10</t>
-  </si>
-  <si>
-    <t>38524</t>
-  </si>
-  <si>
     <t>116922</t>
   </si>
   <si>
     <t>38523</t>
   </si>
   <si>
-    <t>116923</t>
-  </si>
-  <si>
-    <t>38522</t>
-  </si>
-  <si>
-    <t>116930</t>
-  </si>
-  <si>
-    <t>38525</t>
-  </si>
-  <si>
-    <t>116924</t>
-  </si>
-  <si>
-    <t>38515</t>
-  </si>
-  <si>
-    <t>483962</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:22:35</t>
-  </si>
-  <si>
-    <t>38511</t>
-  </si>
-  <si>
-    <t>159976</t>
-  </si>
-  <si>
-    <t>81186218</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:20:18</t>
-  </si>
-  <si>
-    <t>38513</t>
-  </si>
-  <si>
-    <t>116917</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:54</t>
-  </si>
-  <si>
-    <t>38509</t>
-  </si>
-  <si>
-    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
-  </si>
-  <si>
-    <t>116916</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:53</t>
-  </si>
-  <si>
-    <t>38508</t>
-  </si>
-  <si>
-    <t>02741</t>
-  </si>
-  <si>
-    <t>81186214</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:29:45</t>
-  </si>
-  <si>
-    <t>38510</t>
-  </si>
-  <si>
-    <t>67852</t>
-  </si>
-  <si>
-    <t>81186213</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:50:26</t>
-  </si>
-  <si>
-    <t>38505</t>
-  </si>
-  <si>
-    <t>VENETO</t>
-  </si>
-  <si>
-    <t>60689</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:49</t>
-  </si>
-  <si>
-    <t>38491</t>
-  </si>
-  <si>
-    <t>TOTAL EXPRESS</t>
-  </si>
-  <si>
-    <t>60688</t>
-  </si>
-  <si>
-    <t>60687</t>
-  </si>
-  <si>
-    <t>60686</t>
+    <t>PENDENTE</t>
+  </si>
+  <si>
+    <t>483989</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:09:42</t>
   </si>
   <si>
     <t>REJEITADA</t>
@@ -464,6 +587,246 @@
     <t>01/10/2026 11:32:11</t>
   </si>
   <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606761103412015</t>
+  </si>
+  <si>
+    <t>MARIA TELMA FERREIRA (FEMA7834189)</t>
+  </si>
+  <si>
+    <t>Avenida Dom Jaime De Barros Camara</t>
+  </si>
+  <si>
+    <t>795</t>
+  </si>
+  <si>
+    <t>Planalto</t>
+  </si>
+  <si>
+    <t>09895-400</t>
+  </si>
+  <si>
+    <t>Sao Bernardo do Campo</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606751103406107</t>
+  </si>
+  <si>
+    <t>WILLIANE ARRUDA SCHIESARO (AW20250627053803)</t>
+  </si>
+  <si>
+    <t>Rua Prefeito Luis De Magalhaes</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>Peixinhos</t>
+  </si>
+  <si>
+    <t>53300-050</t>
+  </si>
+  <si>
+    <t>Olinda</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607011136737112</t>
+  </si>
+  <si>
+    <t>AMANDA HALEN DE SOUZA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Rua Luiz Scott</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Jardim Iracema/Aldeia</t>
+  </si>
+  <si>
+    <t>06440-260</t>
+  </si>
+  <si>
+    <t>Barueri</t>
+  </si>
+  <si>
+    <t>35261039601246000235550070000154591916765040</t>
+  </si>
+  <si>
+    <t>ADRIANO APARECIDO BELLINI</t>
+  </si>
+  <si>
+    <t>Rua Senador Joaquim Catunda</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Conjunto Habitacional Brigadei</t>
+  </si>
+  <si>
+    <t>04840-300</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607021136755606</t>
+  </si>
+  <si>
+    <t>LETICIA ARAUJO</t>
+  </si>
+  <si>
+    <t>Rua Serra do Mar</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Tres Montanhas</t>
+  </si>
+  <si>
+    <t>06278-080</t>
+  </si>
+  <si>
+    <t>Osasco</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607031138124805</t>
+  </si>
+  <si>
+    <t>MAIARA FERNANDA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>R Lope de Baena</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Jardim Santa Lucrecia</t>
+  </si>
+  <si>
+    <t>05185-170</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606891103494885</t>
+  </si>
+  <si>
+    <t>NATALIA VERAN CAMPOS</t>
+  </si>
+  <si>
+    <t>Rua Valentim Camilo Garcia</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Ponte do Imaruim</t>
+  </si>
+  <si>
+    <t>88130-390</t>
+  </si>
+  <si>
+    <t>Palhoca</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606881103488098</t>
+  </si>
+  <si>
+    <t>GUILHERME VINICIUS</t>
+  </si>
+  <si>
+    <t>Rua Luis Carlos Simonini</t>
+  </si>
+  <si>
+    <t>Mundo</t>
+  </si>
+  <si>
+    <t>Jardim Paraiso</t>
+  </si>
+  <si>
+    <t>18558-052</t>
+  </si>
+  <si>
+    <t>Boituva</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606861103474459</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ DE CAMARGO</t>
+  </si>
+  <si>
+    <t>Avenida Sao Paulo</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Jardim Sao Lucas</t>
+  </si>
+  <si>
+    <t>18767-024</t>
+  </si>
+  <si>
+    <t>Cerqueira Cesar</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606851103469342</t>
+  </si>
+  <si>
+    <t>ANDREZA CAMELO</t>
+  </si>
+  <si>
+    <t>Avenida Joaquim Lourenco de Toledo Bueno</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Guacuri</t>
+  </si>
+  <si>
+    <t>04475-260</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606831103451503</t>
+  </si>
+  <si>
+    <t>PAULO VICTOR</t>
+  </si>
+  <si>
+    <t>Quadra QR 323 Conjunto 5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Samambaia Sul</t>
+  </si>
+  <si>
+    <t>72309-605</t>
+  </si>
+  <si>
+    <t>Brasilia</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
     <t>35261024873172000561550010000606841103462472</t>
   </si>
   <si>
@@ -485,96 +848,6 @@
     <t>Atibaia</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>35261039601246000235550070000154591916765040</t>
-  </si>
-  <si>
-    <t>ADRIANO APARECIDO BELLINI</t>
-  </si>
-  <si>
-    <t>Rua Senador Joaquim Catunda</t>
-  </si>
-  <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Conjunto Habitacional Brigadei</t>
-  </si>
-  <si>
-    <t>04840-300</t>
-  </si>
-  <si>
-    <t>Sao Paulo</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606751103406107</t>
-  </si>
-  <si>
-    <t>WILLIANE ARRUDA SCHIESARO (AW20250627053803)</t>
-  </si>
-  <si>
-    <t>Rua Prefeito Luis De Magalhaes</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>Peixinhos</t>
-  </si>
-  <si>
-    <t>53300-050</t>
-  </si>
-  <si>
-    <t>Olinda</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606851103469342</t>
-  </si>
-  <si>
-    <t>ANDREZA CAMELO</t>
-  </si>
-  <si>
-    <t>Avenida Joaquim Lourenco de Toledo Bueno</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Guacuri</t>
-  </si>
-  <si>
-    <t>04475-260</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606831103451503</t>
-  </si>
-  <si>
-    <t>PAULO VICTOR</t>
-  </si>
-  <si>
-    <t>Quadra QR 323 Conjunto 5</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Samambaia Sul</t>
-  </si>
-  <si>
-    <t>72309-605</t>
-  </si>
-  <si>
-    <t>Brasilia</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
     <t>35261024873172000561550010000606821103440890</t>
   </si>
   <si>
@@ -683,9 +956,6 @@
     <t>Sao Jose</t>
   </si>
   <si>
-    <t>SC</t>
-  </si>
-  <si>
     <t>35261024873172000561550010000606771103417537</t>
   </si>
   <si>
@@ -704,60 +974,321 @@
     <t>22441-140</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606761103412015</t>
-  </si>
-  <si>
-    <t>MARIA TELMA FERREIRA (FEMA7834189)</t>
-  </si>
-  <si>
-    <t>Avenida Dom Jaime De Barros Camara</t>
-  </si>
-  <si>
-    <t>795</t>
-  </si>
-  <si>
-    <t>Planalto</t>
-  </si>
-  <si>
-    <t>09895-400</t>
-  </si>
-  <si>
-    <t>Sao Bernardo do Campo</t>
+    <t>35261002648810000184550010001169231562258086</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
+  </si>
+  <si>
+    <t>RUA SURUBIM</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>CIDADE MONCOES</t>
+  </si>
+  <si>
+    <t>04571-050</t>
+  </si>
+  <si>
+    <t>SAO PAULO</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169301290104950</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606911136582536</t>
+  </si>
+  <si>
+    <t>ROMULO FRATINI</t>
+  </si>
+  <si>
+    <t>Avenida Sao Domingos</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>Vila Morangueira</t>
+  </si>
+  <si>
+    <t>87040-000</t>
+  </si>
+  <si>
+    <t>Maringa</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606921136598847</t>
+  </si>
+  <si>
+    <t>MARIA DAS GRACAS DA SILVA</t>
+  </si>
+  <si>
+    <t>Rua Desembargador Jose Gomes da Costa</t>
+  </si>
+  <si>
+    <t>1890</t>
+  </si>
+  <si>
+    <t>Capim Macio</t>
+  </si>
+  <si>
+    <t>59082-140</t>
+  </si>
+  <si>
+    <t>Natal</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606931136611719</t>
+  </si>
+  <si>
+    <t>MARISA RIBEIRO</t>
+  </si>
+  <si>
+    <t>Rua dos Macunis</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>Vila Madalena</t>
+  </si>
+  <si>
+    <t>05444-001</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169271825808064</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606941136624702</t>
+  </si>
+  <si>
+    <t>ANA BEATRIZ DA SILVA ALVES</t>
+  </si>
+  <si>
+    <t>Rua Marechal Jose Bernardino Bormann</t>
+  </si>
+  <si>
+    <t>1258</t>
+  </si>
+  <si>
+    <t>Bigorrilho</t>
+  </si>
+  <si>
+    <t>80730-350</t>
+  </si>
+  <si>
+    <t>Curitiba</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606951136639510</t>
+  </si>
+  <si>
+    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t>RUA JOAO MOTA</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>JARDIM DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t>37538-714</t>
+  </si>
+  <si>
+    <t>Santa Rita do Sapucai</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606961136652930</t>
+  </si>
+  <si>
+    <t>BEATRIZ FIOLA DE LIMA</t>
+  </si>
+  <si>
+    <t>Rua Aurelia</t>
+  </si>
+  <si>
+    <t>1441</t>
+  </si>
+  <si>
+    <t>Vila Romana</t>
+  </si>
+  <si>
+    <t>05046-001</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606971136668612</t>
+  </si>
+  <si>
+    <t>GERUSA TORRES BLANCH</t>
+  </si>
+  <si>
+    <t>Rua Eduardo</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>Vila Albertina</t>
+  </si>
+  <si>
+    <t>02371-010</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606981136685476</t>
+  </si>
+  <si>
+    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
+  </si>
+  <si>
+    <t>Rua Joao Antonio Biagi</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Aeroporto</t>
+  </si>
+  <si>
+    <t>14302-126</t>
+  </si>
+  <si>
+    <t>Batatais</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606991136703811</t>
+  </si>
+  <si>
+    <t>GRAZIELLA BARROS</t>
+  </si>
+  <si>
+    <t>Rua Corifeu de Azevedo Marques</t>
+  </si>
+  <si>
+    <t>3213</t>
+  </si>
+  <si>
+    <t>Jardim das Industrias</t>
+  </si>
+  <si>
+    <t>12241-040</t>
+  </si>
+  <si>
+    <t>Sao Jose dos Campos</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607001136723068</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
+  </si>
+  <si>
+    <t>Avenida Engenheiro Alberto De Zagottis</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>Jardim Taquaral</t>
+  </si>
+  <si>
+    <t>04675-085</t>
+  </si>
+  <si>
+    <t>35261032014717000189550010000006961933919301</t>
+  </si>
+  <si>
+    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
+  </si>
+  <si>
+    <t>Rodovia Celso Garcia Cid, km 380</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>Jardim Portal de Versalhes 1</t>
+  </si>
+  <si>
+    <t>86055-900</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169211263927089</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606871103481940</t>
+  </si>
+  <si>
+    <t>APARECIDA</t>
+  </si>
+  <si>
+    <t>Avenida Santos Dumont</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Vila Alzira</t>
+  </si>
+  <si>
+    <t>09015-320</t>
+  </si>
+  <si>
+    <t>Santo Andre</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862130000000000</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862140000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862170000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169161629085523</t>
+  </si>
+  <si>
+    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169171204845354</t>
+  </si>
+  <si>
+    <t>04571-000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862180000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000004839620000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169241326233013</t>
   </si>
   <si>
     <t>35261002648810000184550010001169251459162513</t>
   </si>
   <si>
-    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
-  </si>
-  <si>
-    <t>RUA SURUBIM</t>
-  </si>
-  <si>
-    <t>577</t>
-  </si>
-  <si>
-    <t>CIDADE MONCOES</t>
-  </si>
-  <si>
-    <t>04571-050</t>
-  </si>
-  <si>
-    <t>SAO PAULO</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862170000000000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>35261002648810000184550010001169261572131218</t>
   </si>
   <si>
-    <t>35261002648810000184550010001169271825808064</t>
-  </si>
-  <si>
     <t>35261002648810000184550010001169281477045657</t>
   </si>
   <si>
@@ -770,133 +1301,22 @@
     <t>35261002648810000184550010001169201210095383</t>
   </si>
   <si>
-    <t>35261002648810000184550010001169211263927089</t>
-  </si>
-  <si>
     <t>35261002648810000184550010001169221114394191</t>
   </si>
   <si>
-    <t>35261002648810000184550010001169231562258086</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169301290104950</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169241326233013</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000004839620000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862180000000000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169171204845354</t>
-  </si>
-  <si>
-    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
-  </si>
-  <si>
-    <t>04571-000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169161629085523</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862140000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862130000000000</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606891103494885</t>
-  </si>
-  <si>
-    <t>NATALIA VERAN CAMPOS</t>
-  </si>
-  <si>
-    <t>Rua Valentim Camilo Garcia</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Ponte do Imaruim</t>
-  </si>
-  <si>
-    <t>88130-390</t>
-  </si>
-  <si>
-    <t>Palhoca</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606881103488098</t>
-  </si>
-  <si>
-    <t>GUILHERME VINICIUS</t>
-  </si>
-  <si>
-    <t>Rua Luis Carlos Simonini</t>
-  </si>
-  <si>
-    <t>Mundo</t>
-  </si>
-  <si>
-    <t>Jardim Paraiso</t>
-  </si>
-  <si>
-    <t>18558-052</t>
-  </si>
-  <si>
-    <t>Boituva</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606871103481940</t>
-  </si>
-  <si>
-    <t>APARECIDA</t>
-  </si>
-  <si>
-    <t>Avenida Santos Dumont</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Vila Alzira</t>
-  </si>
-  <si>
-    <t>09015-320</t>
-  </si>
-  <si>
-    <t>Santo Andre</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606861103474459</t>
-  </si>
-  <si>
-    <t>ANDRE LUIZ DE CAMARGO</t>
-  </si>
-  <si>
-    <t>Avenida Sao Paulo</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Jardim Sao Lucas</t>
-  </si>
-  <si>
-    <t>18767-024</t>
-  </si>
-  <si>
-    <t>Cerqueira Cesar</t>
+    <t>00000000000000000000000000004839890000000000</t>
   </si>
   <si>
     <t>35261002648810000184550010001169311529968594</t>
   </si>
   <si>
     <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: PEM000002 - SACO 100 MOEDAS - PEBD - LISO - VALIDADE: 01/10/2026 11:32:21. Qtde. Sol.: 1000  Qtde. Disp.: 0</t>
+  </si>
+  <si>
+    <t>35261032014717000189550010000006951807549676</t>
+  </si>
+  <si>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: CRN 003 - DMSO 50 ml - VALIDADE: 01/10/2026 12:02:54. Qtde. Sol.: 12  Qtde. Disp.: 0</t>
   </si>
 </sst>
 </file>
@@ -1342,8 +1762,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E6BFCD-1B4E-4DD7-AF7A-DEA69BD200C2}">
-  <dimension ref="A1:Y41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1F1F03-088A-4B4B-9AD1-40A4873DB0C0}">
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -1362,7 +1782,7 @@
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="35.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="130.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22.5546875" bestFit="1" customWidth="1"/>
@@ -1604,77 +2024,75 @@
         <v>38</v>
       </c>
       <c r="O6" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P6" s="11">
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="W6" s="10" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="O7" s="11">
         <v>1</v>
@@ -1683,29 +2101,29 @@
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -1714,38 +2132,38 @@
         <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O8" s="11">
         <v>1</v>
@@ -1754,66 +2172,68 @@
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>38</v>
@@ -1825,71 +2245,69 @@
         <v>1</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="O10" s="11">
         <v>1</v>
@@ -1898,71 +2316,69 @@
         <v>1</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="O11" s="11">
         <v>1</v>
@@ -1971,29 +2387,29 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -2002,38 +2418,38 @@
         <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O12" s="11">
         <v>1</v>
@@ -2042,29 +2458,29 @@
         <v>1</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4" t="s">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -2073,38 +2489,38 @@
         <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O13" s="11">
         <v>1</v>
@@ -2113,29 +2529,29 @@
         <v>1</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -2144,38 +2560,38 @@
         <v>29</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O14" s="11">
         <v>1</v>
@@ -2184,29 +2600,29 @@
         <v>1</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -2221,32 +2637,32 @@
         <v>31</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="O15" s="11">
         <v>1</v>
@@ -2255,100 +2671,102 @@
         <v>1</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="W15" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="X15" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="X15" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="Y15" s="4" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
+      <c r="A16" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="4" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="O16" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16" s="11">
         <v>1</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>185</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -2357,428 +2775,512 @@
         <v>29</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="4" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="O17" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P17" s="11">
         <v>1</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="B18" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K18" s="9"/>
       <c r="L18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="M18" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N18" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O18" s="11">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="P18" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="4"/>
+      <c r="I19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K19" s="9"/>
       <c r="L19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="M19" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N19" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O19" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P19" s="11">
         <v>1</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
+        <v>278</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="W19" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K20" s="9"/>
       <c r="L20" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="M20" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N20" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O20" s="11">
-        <v>22121</v>
+        <v>1</v>
       </c>
       <c r="P20" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>148</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="M21" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N21" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O21" s="11">
-        <v>11122</v>
+        <v>1</v>
       </c>
       <c r="P21" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="R21" s="4"/>
       <c r="S21" s="4" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>234</v>
+        <v>297</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>148</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K22" s="9"/>
       <c r="L22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N22" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O22" s="11">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="P22" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>232</v>
+        <v>302</v>
       </c>
       <c r="W22" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y22" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y22" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K23" s="9"/>
       <c r="L23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="M23" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="N23" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O23" s="11">
-        <v>224</v>
+        <v>2</v>
       </c>
       <c r="P23" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4" t="s">
-        <v>229</v>
+        <v>306</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>230</v>
+        <v>307</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="W23" s="10" t="s">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="4"/>
@@ -2787,57 +3289,57 @@
       <c r="J24" s="4"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="11">
-        <v>7040</v>
+        <v>6000</v>
       </c>
       <c r="P24" s="11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>241</v>
+        <v>311</v>
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>231</v>
+        <v>314</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>234</v>
+        <v>317</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="4"/>
@@ -2846,57 +3348,57 @@
       <c r="J25" s="4"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O25" s="11">
-        <v>17122</v>
+        <v>4098</v>
       </c>
       <c r="P25" s="11">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>231</v>
+        <v>314</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="W25" s="10" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>234</v>
+        <v>317</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="4"/>
@@ -2905,57 +3407,57 @@
       <c r="J26" s="4"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O26" s="11">
-        <v>8073</v>
+        <v>1</v>
       </c>
       <c r="P26" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>243</v>
+        <v>319</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>231</v>
+        <v>322</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>232</v>
+        <v>323</v>
       </c>
       <c r="W26" s="10" t="s">
-        <v>233</v>
+        <v>324</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>148</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="4"/>
@@ -2964,57 +3466,57 @@
       <c r="J27" s="4"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O27" s="11">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="P27" s="11">
         <v>1</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>244</v>
+        <v>327</v>
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4" t="s">
-        <v>229</v>
+        <v>328</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>230</v>
+        <v>329</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="V27" s="4" t="s">
-        <v>232</v>
+        <v>331</v>
       </c>
       <c r="W27" s="10" t="s">
-        <v>233</v>
+        <v>332</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>234</v>
+        <v>333</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>148</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="4"/>
@@ -3023,57 +3525,57 @@
       <c r="J28" s="4"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="O28" s="11">
-        <v>6000</v>
+        <v>1</v>
       </c>
       <c r="P28" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>245</v>
+        <v>335</v>
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4" t="s">
-        <v>229</v>
+        <v>336</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>230</v>
+        <v>337</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>231</v>
+        <v>338</v>
       </c>
       <c r="V28" s="4" t="s">
-        <v>232</v>
+        <v>339</v>
       </c>
       <c r="W28" s="10" t="s">
-        <v>233</v>
+        <v>340</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="4"/>
@@ -3082,57 +3584,57 @@
       <c r="J29" s="4"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="O29" s="11">
-        <v>4098</v>
+        <v>11122</v>
       </c>
       <c r="P29" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>246</v>
+        <v>341</v>
       </c>
       <c r="R29" s="4"/>
       <c r="S29" s="4" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>231</v>
+        <v>314</v>
       </c>
       <c r="V29" s="4" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="X29" s="4" t="s">
-        <v>234</v>
+        <v>317</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>106</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="4"/>
@@ -3141,57 +3643,57 @@
       <c r="J30" s="4"/>
       <c r="K30" s="9"/>
       <c r="L30" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O30" s="11">
-        <v>7048</v>
+        <v>1</v>
       </c>
       <c r="P30" s="11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>247</v>
+        <v>342</v>
       </c>
       <c r="R30" s="4"/>
       <c r="S30" s="4" t="s">
-        <v>229</v>
+        <v>343</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>230</v>
+        <v>344</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="V30" s="4" t="s">
-        <v>232</v>
+        <v>346</v>
       </c>
       <c r="W30" s="10" t="s">
-        <v>233</v>
+        <v>347</v>
       </c>
       <c r="X30" s="4" t="s">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="Y30" s="4" t="s">
-        <v>148</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="4"/>
@@ -3200,45 +3702,57 @@
       <c r="J31" s="4"/>
       <c r="K31" s="9"/>
       <c r="L31" s="4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O31" s="11">
         <v>4</v>
       </c>
       <c r="P31" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
+      <c r="S31" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="T31" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="V31" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="W31" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y31" s="4" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>111</v>
-      </c>
+      <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="4"/>
@@ -3247,45 +3761,57 @@
       <c r="J32" s="4"/>
       <c r="K32" s="9"/>
       <c r="L32" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="O32" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P32" s="11">
         <v>1</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>249</v>
+        <v>356</v>
       </c>
       <c r="R32" s="4"/>
       <c r="S32" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
+        <v>357</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="W32" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="X32" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y32" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="4"/>
@@ -3294,59 +3820,57 @@
       <c r="J33" s="4"/>
       <c r="K33" s="9"/>
       <c r="L33" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M33" s="4"/>
       <c r="N33" s="4" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="O33" s="11">
-        <v>14177</v>
+        <v>1</v>
       </c>
       <c r="P33" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="R33" s="4" t="s">
-        <v>251</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="R33" s="4"/>
       <c r="S33" s="4" t="s">
-        <v>229</v>
+        <v>363</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>230</v>
+        <v>364</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="V33" s="4" t="s">
-        <v>232</v>
+        <v>366</v>
       </c>
       <c r="W33" s="10" t="s">
-        <v>252</v>
+        <v>367</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="4"/>
@@ -3355,61 +3879,57 @@
       <c r="J34" s="4"/>
       <c r="K34" s="9"/>
       <c r="L34" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="O34" s="11">
-        <v>13107</v>
+        <v>1</v>
       </c>
       <c r="P34" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="R34" s="4" t="s">
-        <v>251</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="R34" s="4"/>
       <c r="S34" s="4" t="s">
-        <v>229</v>
+        <v>369</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>230</v>
+        <v>370</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="W34" s="10" t="s">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="Y34" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>122</v>
-      </c>
+      <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="4"/>
@@ -3418,47 +3938,57 @@
       <c r="J35" s="4"/>
       <c r="K35" s="9"/>
       <c r="L35" s="4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="O35" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P35" s="11">
         <v>1</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>254</v>
+        <v>375</v>
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="10"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
+        <v>376</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="V35" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="W35" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="X35" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y35" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="4"/>
@@ -3467,45 +3997,57 @@
       <c r="J36" s="4"/>
       <c r="K36" s="9"/>
       <c r="L36" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O36" s="11">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="P36" s="11">
         <v>1</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>255</v>
+        <v>382</v>
       </c>
       <c r="R36" s="4"/>
       <c r="S36" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
+        <v>383</v>
+      </c>
+      <c r="T36" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="V36" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="W36" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="X36" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y36" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="4"/>
@@ -3514,57 +4056,57 @@
       <c r="J37" s="4"/>
       <c r="K37" s="9"/>
       <c r="L37" s="4" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="O37" s="11">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P37" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>256</v>
+        <v>388</v>
       </c>
       <c r="R37" s="4"/>
       <c r="S37" s="4" t="s">
-        <v>257</v>
+        <v>389</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>258</v>
+        <v>390</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>259</v>
+        <v>391</v>
       </c>
       <c r="V37" s="4" t="s">
-        <v>260</v>
+        <v>392</v>
       </c>
       <c r="W37" s="10" t="s">
-        <v>261</v>
+        <v>393</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>262</v>
+        <v>394</v>
       </c>
       <c r="Y37" s="4" t="s">
-        <v>214</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="4"/>
@@ -3573,57 +4115,57 @@
       <c r="J38" s="4"/>
       <c r="K38" s="9"/>
       <c r="L38" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="O38" s="11">
-        <v>1</v>
+        <v>8073</v>
       </c>
       <c r="P38" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>263</v>
+        <v>395</v>
       </c>
       <c r="R38" s="4"/>
       <c r="S38" s="4" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="T38" s="4" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="V38" s="4" t="s">
-        <v>267</v>
+        <v>315</v>
       </c>
       <c r="W38" s="10" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="Y38" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="4"/>
@@ -3632,11 +4174,11 @@
       <c r="J39" s="4"/>
       <c r="K39" s="9"/>
       <c r="L39" s="4" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="O39" s="11">
         <v>1</v>
@@ -3645,44 +4187,46 @@
         <v>1</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>270</v>
+        <v>396</v>
       </c>
       <c r="R39" s="4"/>
       <c r="S39" s="4" t="s">
-        <v>271</v>
+        <v>397</v>
       </c>
       <c r="T39" s="4" t="s">
-        <v>272</v>
+        <v>398</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>273</v>
+        <v>399</v>
       </c>
       <c r="V39" s="4" t="s">
-        <v>274</v>
+        <v>400</v>
       </c>
       <c r="W39" s="10" t="s">
-        <v>275</v>
+        <v>401</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>276</v>
+        <v>402</v>
       </c>
       <c r="Y39" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
+      <c r="A40" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="B40" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="4"/>
@@ -3698,50 +4242,40 @@
         <v>134</v>
       </c>
       <c r="O40" s="11">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="P40" s="11">
         <v>1</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>277</v>
+        <v>403</v>
       </c>
       <c r="R40" s="4"/>
       <c r="S40" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="T40" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="U40" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="V40" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="W40" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="X40" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="Y40" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="B41" s="4" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="4"/>
@@ -3749,28 +4283,896 @@
       <c r="I41" s="9"/>
       <c r="J41" s="4"/>
       <c r="K41" s="9"/>
-      <c r="L41" s="4"/>
+      <c r="L41" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
+      <c r="N41" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="O41" s="11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P41" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="S41" s="4"/>
+        <v>405</v>
+      </c>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4" t="s">
+        <v>404</v>
+      </c>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
       <c r="W41" s="10"/>
       <c r="X41" s="4"/>
       <c r="Y41" s="4"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O42" s="11">
+        <v>4</v>
+      </c>
+      <c r="P42" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="10"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="O43" s="11">
+        <v>13107</v>
+      </c>
+      <c r="P43" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q43" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W43" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X43" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y43" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="O44" s="11">
+        <v>14177</v>
+      </c>
+      <c r="P44" s="11">
+        <v>17</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="S44" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T44" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V44" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W44" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="X44" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y44" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O45" s="11">
+        <v>10</v>
+      </c>
+      <c r="P45" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O46" s="11">
+        <v>4</v>
+      </c>
+      <c r="P46" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="10"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O47" s="11">
+        <v>7048</v>
+      </c>
+      <c r="P47" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T47" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U47" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V47" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W47" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X47" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y47" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O48" s="11">
+        <v>180</v>
+      </c>
+      <c r="P48" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T48" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V48" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W48" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X48" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y48" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O49" s="11">
+        <v>22121</v>
+      </c>
+      <c r="P49" s="11">
+        <v>17</v>
+      </c>
+      <c r="Q49" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T49" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V49" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W49" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X49" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y49" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O50" s="11">
+        <v>61</v>
+      </c>
+      <c r="P50" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q50" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T50" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V50" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W50" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X50" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y50" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O51" s="11">
+        <v>224</v>
+      </c>
+      <c r="P51" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T51" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V51" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W51" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X51" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y51" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O52" s="11">
+        <v>7040</v>
+      </c>
+      <c r="P52" s="11">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T52" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V52" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W52" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X52" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y52" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O53" s="11">
+        <v>17122</v>
+      </c>
+      <c r="P53" s="11">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T53" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V53" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W53" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X53" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y53" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O54" s="11">
+        <v>3000</v>
+      </c>
+      <c r="P54" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="T54" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="V54" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="W54" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="X54" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y54" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" s="9"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="11">
+        <v>300</v>
+      </c>
+      <c r="P55" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="10"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="11">
+        <v>0</v>
+      </c>
+      <c r="P56" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="R56" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="11">
+        <v>0</v>
+      </c>
+      <c r="P57" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="10"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/status_saida/operacional/status_out_2026.xlsx
+++ b/data/status_saida/operacional/status_out_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opera\Desktop\app\dashboard_operacao\data\status_saida\operacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EFB4020-6986-4C24-8FC5-A35250EFF697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{469E7C90-BC58-417E-8074-3B489F043E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00452EF5-AB32-4BC4-BE8F-4ED0999574BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B293A39-4CF1-4375-A01C-1D3351EF5A67}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="444">
   <si>
     <t>Relatório de Pedidos  Geral</t>
   </si>
@@ -161,6 +161,420 @@
     <t>60675</t>
   </si>
   <si>
+    <t>60691</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:35</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:08:22</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:09:49</t>
+  </si>
+  <si>
+    <t>38526</t>
+  </si>
+  <si>
+    <t>26671</t>
+  </si>
+  <si>
+    <t>JMS CARGO (JADLOG)</t>
+  </si>
+  <si>
+    <t>60692</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:36</t>
+  </si>
+  <si>
+    <t>60693</t>
+  </si>
+  <si>
+    <t>60694</t>
+  </si>
+  <si>
+    <t>60695</t>
+  </si>
+  <si>
+    <t>60696</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:37</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:22:46</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:25:13</t>
+  </si>
+  <si>
+    <t>38527</t>
+  </si>
+  <si>
+    <t>26674</t>
+  </si>
+  <si>
+    <t>CORREIOS VETTORE</t>
+  </si>
+  <si>
+    <t>60697</t>
+  </si>
+  <si>
+    <t>60698</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:47:44</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:48:36</t>
+  </si>
+  <si>
+    <t>38529</t>
+  </si>
+  <si>
+    <t>200001873233408</t>
+  </si>
+  <si>
+    <t>15459</t>
+  </si>
+  <si>
+    <t>RHINO AUTOPARTS DISTRIBUIDORA E IMPORTADORA DE AUTO PEÇAS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:50:08</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:04:56</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:06:03</t>
+  </si>
+  <si>
+    <t>38507</t>
+  </si>
+  <si>
+    <t>26673</t>
+  </si>
+  <si>
+    <t>60699</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:38</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:14:06</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:17:33</t>
+  </si>
+  <si>
+    <t>38530</t>
+  </si>
+  <si>
+    <t>26678</t>
+  </si>
+  <si>
+    <t>SHOPEE EXPRESSS</t>
+  </si>
+  <si>
+    <t>60689</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:49</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:05:53</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:06:51</t>
+  </si>
+  <si>
+    <t>38491</t>
+  </si>
+  <si>
+    <t>26675</t>
+  </si>
+  <si>
+    <t>TOTAL EXPRESS</t>
+  </si>
+  <si>
+    <t>60688</t>
+  </si>
+  <si>
+    <t>60687</t>
+  </si>
+  <si>
+    <t>60686</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:48</t>
+  </si>
+  <si>
+    <t>60685</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:12:54</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:14:25</t>
+  </si>
+  <si>
+    <t>38492</t>
+  </si>
+  <si>
+    <t>60684</t>
+  </si>
+  <si>
+    <t>166546891073601</t>
+  </si>
+  <si>
+    <t>60683</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:50:50</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:53:39</t>
+  </si>
+  <si>
+    <t>38494</t>
+  </si>
+  <si>
+    <t>166550891492101</t>
+  </si>
+  <si>
+    <t>60682</t>
+  </si>
+  <si>
+    <t>60681</t>
+  </si>
+  <si>
+    <t>60680</t>
+  </si>
+  <si>
+    <t>60679</t>
+  </si>
+  <si>
+    <t>60678</t>
+  </si>
+  <si>
+    <t>60677</t>
+  </si>
+  <si>
+    <t>EM SEPARACAO</t>
+  </si>
+  <si>
+    <t>116927</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:46</t>
+  </si>
+  <si>
+    <t>38516</t>
+  </si>
+  <si>
+    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
+  </si>
+  <si>
+    <t>116921</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:10</t>
+  </si>
+  <si>
+    <t>38524</t>
+  </si>
+  <si>
+    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>116922</t>
+  </si>
+  <si>
+    <t>38523</t>
+  </si>
+  <si>
+    <t>116923</t>
+  </si>
+  <si>
+    <t>38522</t>
+  </si>
+  <si>
+    <t>116930</t>
+  </si>
+  <si>
+    <t>38525</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:40</t>
+  </si>
+  <si>
+    <t>38532</t>
+  </si>
+  <si>
+    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
+  </si>
+  <si>
+    <t>116918</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:09</t>
+  </si>
+  <si>
+    <t>38521</t>
+  </si>
+  <si>
+    <t>67852</t>
+  </si>
+  <si>
+    <t>81186213</t>
+  </si>
+  <si>
+    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:50:26</t>
+  </si>
+  <si>
+    <t>38505</t>
+  </si>
+  <si>
+    <t>VENETO</t>
+  </si>
+  <si>
+    <t>02741</t>
+  </si>
+  <si>
+    <t>81186214</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:29:45</t>
+  </si>
+  <si>
+    <t>38510</t>
+  </si>
+  <si>
+    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
+  </si>
+  <si>
+    <t>Doação JSA-Zandoná</t>
+  </si>
+  <si>
+    <t>81186217</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:02:42</t>
+  </si>
+  <si>
+    <t>38512</t>
+  </si>
+  <si>
+    <t>116916</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:53</t>
+  </si>
+  <si>
+    <t>38508</t>
+  </si>
+  <si>
+    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
+  </si>
+  <si>
+    <t>116917</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:54</t>
+  </si>
+  <si>
+    <t>38509</t>
+  </si>
+  <si>
+    <t>159976</t>
+  </si>
+  <si>
+    <t>81186218</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:20:18</t>
+  </si>
+  <si>
+    <t>38513</t>
+  </si>
+  <si>
+    <t>116924</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:45</t>
+  </si>
+  <si>
+    <t>38515</t>
+  </si>
+  <si>
+    <t>116925</t>
+  </si>
+  <si>
+    <t>38517</t>
+  </si>
+  <si>
+    <t>116926</t>
+  </si>
+  <si>
+    <t>38514</t>
+  </si>
+  <si>
+    <t>116928</t>
+  </si>
+  <si>
+    <t>38519</t>
+  </si>
+  <si>
+    <t>116929</t>
+  </si>
+  <si>
+    <t>38518</t>
+  </si>
+  <si>
+    <t>116920</t>
+  </si>
+  <si>
+    <t>38520</t>
+  </si>
+  <si>
+    <t>EXPEDIDO</t>
+  </si>
+  <si>
+    <t>60700</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:31:36</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:33:09</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:15:26</t>
+  </si>
+  <si>
+    <t>38531</t>
+  </si>
+  <si>
+    <t>26677</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - ML FLEX</t>
+  </si>
+  <si>
     <t>60701</t>
   </si>
   <si>
@@ -173,6 +587,9 @@
     <t>01/10/2026 12:28:24</t>
   </si>
   <si>
+    <t>01/10/2026 13:16:14</t>
+  </si>
+  <si>
     <t>38528</t>
   </si>
   <si>
@@ -182,402 +599,36 @@
     <t>TM TRANSPORTE - SHOPEE FLEX</t>
   </si>
   <si>
-    <t>200001873233408</t>
-  </si>
-  <si>
-    <t>15459</t>
-  </si>
-  <si>
-    <t>RHINO AUTOPARTS DISTRIBUIDORA E IMPORTADORA DE AUTO PEÇAS LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:50:08</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:04:56</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:06:03</t>
-  </si>
-  <si>
-    <t>38507</t>
-  </si>
-  <si>
-    <t>26673</t>
-  </si>
-  <si>
     <t>60702</t>
   </si>
   <si>
     <t>60703</t>
   </si>
   <si>
-    <t>60689</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:49</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:05:53</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:06:51</t>
-  </si>
-  <si>
-    <t>38491</t>
-  </si>
-  <si>
-    <t>26675</t>
-  </si>
-  <si>
-    <t>TOTAL EXPRESS</t>
-  </si>
-  <si>
-    <t>60688</t>
-  </si>
-  <si>
-    <t>60686</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:48</t>
-  </si>
-  <si>
-    <t>60685</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:12:54</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:14:25</t>
-  </si>
-  <si>
-    <t>38492</t>
-  </si>
-  <si>
-    <t>26674</t>
-  </si>
-  <si>
-    <t>CORREIOS VETTORE</t>
-  </si>
-  <si>
-    <t>166546891073601</t>
-  </si>
-  <si>
-    <t>60683</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:50:50</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:53:39</t>
-  </si>
-  <si>
-    <t>38494</t>
-  </si>
-  <si>
-    <t>26671</t>
-  </si>
-  <si>
-    <t>JMS CARGO (JADLOG)</t>
-  </si>
-  <si>
-    <t>60684</t>
-  </si>
-  <si>
-    <t>166550891492101</t>
-  </si>
-  <si>
-    <t>60682</t>
-  </si>
-  <si>
-    <t>60681</t>
-  </si>
-  <si>
-    <t>60680</t>
-  </si>
-  <si>
-    <t>60679</t>
-  </si>
-  <si>
-    <t>60678</t>
-  </si>
-  <si>
-    <t>60677</t>
-  </si>
-  <si>
-    <t>EM SEPARACAO</t>
-  </si>
-  <si>
-    <t>116923</t>
-  </si>
-  <si>
-    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:10</t>
-  </si>
-  <si>
-    <t>38522</t>
-  </si>
-  <si>
-    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>116930</t>
-  </si>
-  <si>
-    <t>38525</t>
-  </si>
-  <si>
-    <t>60691</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:35</t>
-  </si>
-  <si>
-    <t>38526</t>
-  </si>
-  <si>
-    <t>60692</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:36</t>
-  </si>
-  <si>
-    <t>60693</t>
-  </si>
-  <si>
-    <t>116927</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:46</t>
-  </si>
-  <si>
-    <t>38516</t>
-  </si>
-  <si>
-    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
-  </si>
-  <si>
-    <t>60694</t>
-  </si>
-  <si>
-    <t>60695</t>
-  </si>
-  <si>
-    <t>60696</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:37</t>
-  </si>
-  <si>
-    <t>38527</t>
-  </si>
-  <si>
-    <t>60697</t>
-  </si>
-  <si>
-    <t>60698</t>
-  </si>
-  <si>
-    <t>38529</t>
-  </si>
-  <si>
-    <t>60699</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:38</t>
-  </si>
-  <si>
-    <t>38530</t>
-  </si>
-  <si>
-    <t>SHOPEE EXPRESSS</t>
-  </si>
-  <si>
-    <t>60700</t>
-  </si>
-  <si>
-    <t>38531</t>
-  </si>
-  <si>
-    <t>TM TRANSPORTE - ML FLEX</t>
-  </si>
-  <si>
-    <t>696</t>
-  </si>
-  <si>
-    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:40</t>
-  </si>
-  <si>
-    <t>38532</t>
-  </si>
-  <si>
-    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
-  </si>
-  <si>
-    <t>116921</t>
-  </si>
-  <si>
-    <t>38524</t>
-  </si>
-  <si>
-    <t>60687</t>
-  </si>
-  <si>
-    <t>67852</t>
-  </si>
-  <si>
-    <t>81186213</t>
-  </si>
-  <si>
-    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:50:26</t>
-  </si>
-  <si>
-    <t>38505</t>
-  </si>
-  <si>
-    <t>VENETO</t>
-  </si>
-  <si>
-    <t>02741</t>
-  </si>
-  <si>
-    <t>81186214</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:29:45</t>
-  </si>
-  <si>
-    <t>38510</t>
-  </si>
-  <si>
-    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
-  </si>
-  <si>
-    <t>Doação JSA-Zandoná</t>
-  </si>
-  <si>
-    <t>81186217</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:02:42</t>
-  </si>
-  <si>
-    <t>38512</t>
-  </si>
-  <si>
-    <t>116916</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:53</t>
-  </si>
-  <si>
-    <t>38508</t>
-  </si>
-  <si>
-    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
-  </si>
-  <si>
-    <t>116917</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:54</t>
-  </si>
-  <si>
-    <t>38509</t>
-  </si>
-  <si>
-    <t>159976</t>
-  </si>
-  <si>
-    <t>81186218</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:20:18</t>
-  </si>
-  <si>
-    <t>38513</t>
-  </si>
-  <si>
-    <t>483962</t>
+    <t>PENDENTE</t>
+  </si>
+  <si>
+    <t>81186219</t>
   </si>
   <si>
     <t>01/10/2026 10:22:35</t>
   </si>
   <si>
-    <t>38511</t>
-  </si>
-  <si>
-    <t>116924</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:45</t>
-  </si>
-  <si>
-    <t>38515</t>
-  </si>
-  <si>
-    <t>116925</t>
-  </si>
-  <si>
-    <t>38517</t>
-  </si>
-  <si>
-    <t>116926</t>
-  </si>
-  <si>
-    <t>38514</t>
-  </si>
-  <si>
-    <t>116928</t>
-  </si>
-  <si>
-    <t>38519</t>
-  </si>
-  <si>
-    <t>116929</t>
-  </si>
-  <si>
-    <t>38518</t>
-  </si>
-  <si>
-    <t>116918</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:09</t>
-  </si>
-  <si>
-    <t>38521</t>
-  </si>
-  <si>
-    <t>116920</t>
-  </si>
-  <si>
-    <t>38520</t>
-  </si>
-  <si>
-    <t>116922</t>
-  </si>
-  <si>
-    <t>38523</t>
-  </si>
-  <si>
-    <t>PENDENTE</t>
-  </si>
-  <si>
-    <t>483989</t>
+    <t>81186215</t>
   </si>
   <si>
     <t>01/10/2026 12:09:42</t>
   </si>
   <si>
+    <t>PED.COT.55569</t>
+  </si>
+  <si>
+    <t>81186225</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:27:32</t>
+  </si>
+  <si>
     <t>REJEITADA</t>
   </si>
   <si>
@@ -638,6 +689,609 @@
     <t>PE</t>
   </si>
   <si>
+    <t>35261024873172000561550010000606911136582536</t>
+  </si>
+  <si>
+    <t>ROMULO FRATINI</t>
+  </si>
+  <si>
+    <t>Avenida Sao Domingos</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>Vila Morangueira</t>
+  </si>
+  <si>
+    <t>87040-000</t>
+  </si>
+  <si>
+    <t>Maringa</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606921136598847</t>
+  </si>
+  <si>
+    <t>MARIA DAS GRACAS DA SILVA</t>
+  </si>
+  <si>
+    <t>Rua Desembargador Jose Gomes da Costa</t>
+  </si>
+  <si>
+    <t>1890</t>
+  </si>
+  <si>
+    <t>Capim Macio</t>
+  </si>
+  <si>
+    <t>59082-140</t>
+  </si>
+  <si>
+    <t>Natal</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606931136611719</t>
+  </si>
+  <si>
+    <t>MARISA RIBEIRO</t>
+  </si>
+  <si>
+    <t>Rua dos Macunis</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>Vila Madalena</t>
+  </si>
+  <si>
+    <t>05444-001</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606941136624702</t>
+  </si>
+  <si>
+    <t>ANA BEATRIZ DA SILVA ALVES</t>
+  </si>
+  <si>
+    <t>Rua Marechal Jose Bernardino Bormann</t>
+  </si>
+  <si>
+    <t>1258</t>
+  </si>
+  <si>
+    <t>Bigorrilho</t>
+  </si>
+  <si>
+    <t>80730-350</t>
+  </si>
+  <si>
+    <t>Curitiba</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606951136639510</t>
+  </si>
+  <si>
+    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t>RUA JOAO MOTA</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>JARDIM DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t>37538-714</t>
+  </si>
+  <si>
+    <t>Santa Rita do Sapucai</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606961136652930</t>
+  </si>
+  <si>
+    <t>BEATRIZ FIOLA DE LIMA</t>
+  </si>
+  <si>
+    <t>Rua Aurelia</t>
+  </si>
+  <si>
+    <t>1441</t>
+  </si>
+  <si>
+    <t>Vila Romana</t>
+  </si>
+  <si>
+    <t>05046-001</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606971136668612</t>
+  </si>
+  <si>
+    <t>GERUSA TORRES BLANCH</t>
+  </si>
+  <si>
+    <t>Rua Eduardo</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>Vila Albertina</t>
+  </si>
+  <si>
+    <t>02371-010</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606981136685476</t>
+  </si>
+  <si>
+    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
+  </si>
+  <si>
+    <t>Rua Joao Antonio Biagi</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Aeroporto</t>
+  </si>
+  <si>
+    <t>14302-126</t>
+  </si>
+  <si>
+    <t>Batatais</t>
+  </si>
+  <si>
+    <t>35261039601246000235550070000154591916765040</t>
+  </si>
+  <si>
+    <t>ADRIANO APARECIDO BELLINI</t>
+  </si>
+  <si>
+    <t>Rua Senador Joaquim Catunda</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Conjunto Habitacional Brigadei</t>
+  </si>
+  <si>
+    <t>04840-300</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606991136703811</t>
+  </si>
+  <si>
+    <t>GRAZIELLA BARROS</t>
+  </si>
+  <si>
+    <t>Rua Corifeu de Azevedo Marques</t>
+  </si>
+  <si>
+    <t>3213</t>
+  </si>
+  <si>
+    <t>Jardim das Industrias</t>
+  </si>
+  <si>
+    <t>12241-040</t>
+  </si>
+  <si>
+    <t>Sao Jose dos Campos</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606891103494885</t>
+  </si>
+  <si>
+    <t>NATALIA VERAN CAMPOS</t>
+  </si>
+  <si>
+    <t>Rua Valentim Camilo Garcia</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Ponte do Imaruim</t>
+  </si>
+  <si>
+    <t>88130-390</t>
+  </si>
+  <si>
+    <t>Palhoca</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606881103488098</t>
+  </si>
+  <si>
+    <t>GUILHERME VINICIUS</t>
+  </si>
+  <si>
+    <t>Rua Luis Carlos Simonini</t>
+  </si>
+  <si>
+    <t>Mundo</t>
+  </si>
+  <si>
+    <t>Jardim Paraiso</t>
+  </si>
+  <si>
+    <t>18558-052</t>
+  </si>
+  <si>
+    <t>Boituva</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606871103481940</t>
+  </si>
+  <si>
+    <t>APARECIDA</t>
+  </si>
+  <si>
+    <t>Avenida Santos Dumont</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Vila Alzira</t>
+  </si>
+  <si>
+    <t>09015-320</t>
+  </si>
+  <si>
+    <t>Santo Andre</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606861103474459</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ DE CAMARGO</t>
+  </si>
+  <si>
+    <t>Avenida Sao Paulo</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Jardim Sao Lucas</t>
+  </si>
+  <si>
+    <t>18767-024</t>
+  </si>
+  <si>
+    <t>Cerqueira Cesar</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606851103469342</t>
+  </si>
+  <si>
+    <t>ANDREZA CAMELO</t>
+  </si>
+  <si>
+    <t>Avenida Joaquim Lourenco de Toledo Bueno</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Guacuri</t>
+  </si>
+  <si>
+    <t>04475-260</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606841103462472</t>
+  </si>
+  <si>
+    <t>ANA PAULA BENTO GALLO</t>
+  </si>
+  <si>
+    <t>Rua America</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Atibaia jardim</t>
+  </si>
+  <si>
+    <t>12942-170</t>
+  </si>
+  <si>
+    <t>Atibaia</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606831103451503</t>
+  </si>
+  <si>
+    <t>PAULO VICTOR</t>
+  </si>
+  <si>
+    <t>Quadra QR 323 Conjunto 5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Samambaia Sul</t>
+  </si>
+  <si>
+    <t>72309-605</t>
+  </si>
+  <si>
+    <t>Brasilia</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606821103440890</t>
+  </si>
+  <si>
+    <t>HERICA SANTOS</t>
+  </si>
+  <si>
+    <t>Rua Messina</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Jardim Carioca</t>
+  </si>
+  <si>
+    <t>21921-360</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606811103436097</t>
+  </si>
+  <si>
+    <t>VALERIA ARAUJO</t>
+  </si>
+  <si>
+    <t>SQN 111 Bloco C</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Asa Norte</t>
+  </si>
+  <si>
+    <t>70754-030</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606801103431284</t>
+  </si>
+  <si>
+    <t>GLAUCIA TEREZA BATISTA</t>
+  </si>
+  <si>
+    <t>Rua Jose Ede</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>36200-018</t>
+  </si>
+  <si>
+    <t>Barbacena</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606791103427391</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>Rua Quatorze</t>
+  </si>
+  <si>
+    <t>906</t>
+  </si>
+  <si>
+    <t>Ilha dos Araujos</t>
+  </si>
+  <si>
+    <t>35020-720</t>
+  </si>
+  <si>
+    <t>Governador Valadares</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606781103422546</t>
+  </si>
+  <si>
+    <t>NICOLE BALDO MENDES</t>
+  </si>
+  <si>
+    <t>Rua Maria Manchen de Souza</t>
+  </si>
+  <si>
+    <t>210 apto 1</t>
+  </si>
+  <si>
+    <t>Kobrasol</t>
+  </si>
+  <si>
+    <t>88102-500</t>
+  </si>
+  <si>
+    <t>Sao Jose</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606771103417537</t>
+  </si>
+  <si>
+    <t>NADIA MONTAGNA</t>
+  </si>
+  <si>
+    <t>General Artigas</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Leblon</t>
+  </si>
+  <si>
+    <t>22441-140</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169271825808064</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
+  </si>
+  <si>
+    <t>RUA SURUBIM</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>CIDADE MONCOES</t>
+  </si>
+  <si>
+    <t>04571-050</t>
+  </si>
+  <si>
+    <t>SAO PAULO</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169211263927089</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169221114394191</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169231562258086</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169301290104950</t>
+  </si>
+  <si>
+    <t>35261032014717000189550010000006961933919301</t>
+  </si>
+  <si>
+    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
+  </si>
+  <si>
+    <t>Rodovia Celso Garcia Cid, km 380</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>Jardim Portal de Versalhes 1</t>
+  </si>
+  <si>
+    <t>86055-900</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169181828741727</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862130000000000</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862140000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862170000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169161629085523</t>
+  </si>
+  <si>
+    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169171204845354</t>
+  </si>
+  <si>
+    <t>04571-000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862180000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169241326233013</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169251459162513</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169261572131218</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169281477045657</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169291699333540</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169201210095383</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607001136723068</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
+  </si>
+  <si>
+    <t>Avenida Engenheiro Alberto De Zagottis</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>Jardim Taquaral</t>
+  </si>
+  <si>
+    <t>04675-085</t>
+  </si>
+  <si>
     <t>35261024873172000561550010000607011136737112</t>
   </si>
   <si>
@@ -659,27 +1313,6 @@
     <t>Barueri</t>
   </si>
   <si>
-    <t>35261039601246000235550070000154591916765040</t>
-  </si>
-  <si>
-    <t>ADRIANO APARECIDO BELLINI</t>
-  </si>
-  <si>
-    <t>Rua Senador Joaquim Catunda</t>
-  </si>
-  <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Conjunto Habitacional Brigadei</t>
-  </si>
-  <si>
-    <t>04840-300</t>
-  </si>
-  <si>
-    <t>Sao Paulo</t>
-  </si>
-  <si>
     <t>35261024873172000561550010000607021136755606</t>
   </si>
   <si>
@@ -719,592 +1352,13 @@
     <t>05185-170</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606891103494885</t>
-  </si>
-  <si>
-    <t>NATALIA VERAN CAMPOS</t>
-  </si>
-  <si>
-    <t>Rua Valentim Camilo Garcia</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Ponte do Imaruim</t>
-  </si>
-  <si>
-    <t>88130-390</t>
-  </si>
-  <si>
-    <t>Palhoca</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606881103488098</t>
-  </si>
-  <si>
-    <t>GUILHERME VINICIUS</t>
-  </si>
-  <si>
-    <t>Rua Luis Carlos Simonini</t>
-  </si>
-  <si>
-    <t>Mundo</t>
-  </si>
-  <si>
-    <t>Jardim Paraiso</t>
-  </si>
-  <si>
-    <t>18558-052</t>
-  </si>
-  <si>
-    <t>Boituva</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606861103474459</t>
-  </si>
-  <si>
-    <t>ANDRE LUIZ DE CAMARGO</t>
-  </si>
-  <si>
-    <t>Avenida Sao Paulo</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Jardim Sao Lucas</t>
-  </si>
-  <si>
-    <t>18767-024</t>
-  </si>
-  <si>
-    <t>Cerqueira Cesar</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606851103469342</t>
-  </si>
-  <si>
-    <t>ANDREZA CAMELO</t>
-  </si>
-  <si>
-    <t>Avenida Joaquim Lourenco de Toledo Bueno</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Guacuri</t>
-  </si>
-  <si>
-    <t>04475-260</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606831103451503</t>
-  </si>
-  <si>
-    <t>PAULO VICTOR</t>
-  </si>
-  <si>
-    <t>Quadra QR 323 Conjunto 5</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Samambaia Sul</t>
-  </si>
-  <si>
-    <t>72309-605</t>
-  </si>
-  <si>
-    <t>Brasilia</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606841103462472</t>
-  </si>
-  <si>
-    <t>ANA PAULA BENTO GALLO</t>
-  </si>
-  <si>
-    <t>Rua America</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Atibaia jardim</t>
-  </si>
-  <si>
-    <t>12942-170</t>
-  </si>
-  <si>
-    <t>Atibaia</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606821103440890</t>
-  </si>
-  <si>
-    <t>HERICA SANTOS</t>
-  </si>
-  <si>
-    <t>Rua Messina</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Jardim Carioca</t>
-  </si>
-  <si>
-    <t>21921-360</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606811103436097</t>
-  </si>
-  <si>
-    <t>VALERIA ARAUJO</t>
-  </si>
-  <si>
-    <t>SQN 111 Bloco C</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Asa Norte</t>
-  </si>
-  <si>
-    <t>70754-030</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606801103431284</t>
-  </si>
-  <si>
-    <t>GLAUCIA TEREZA BATISTA</t>
-  </si>
-  <si>
-    <t>Rua Jose Ede</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>36200-018</t>
-  </si>
-  <si>
-    <t>Barbacena</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606791103427391</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>Rua Quatorze</t>
-  </si>
-  <si>
-    <t>906</t>
-  </si>
-  <si>
-    <t>Ilha dos Araujos</t>
-  </si>
-  <si>
-    <t>35020-720</t>
-  </si>
-  <si>
-    <t>Governador Valadares</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606781103422546</t>
-  </si>
-  <si>
-    <t>NICOLE BALDO MENDES</t>
-  </si>
-  <si>
-    <t>Rua Maria Manchen de Souza</t>
-  </si>
-  <si>
-    <t>210 apto 1</t>
-  </si>
-  <si>
-    <t>Kobrasol</t>
-  </si>
-  <si>
-    <t>88102-500</t>
-  </si>
-  <si>
-    <t>Sao Jose</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606771103417537</t>
-  </si>
-  <si>
-    <t>NADIA MONTAGNA</t>
-  </si>
-  <si>
-    <t>General Artigas</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Leblon</t>
-  </si>
-  <si>
-    <t>22441-140</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169231562258086</t>
-  </si>
-  <si>
-    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
-  </si>
-  <si>
-    <t>RUA SURUBIM</t>
-  </si>
-  <si>
-    <t>577</t>
-  </si>
-  <si>
-    <t>CIDADE MONCOES</t>
-  </si>
-  <si>
-    <t>04571-050</t>
-  </si>
-  <si>
-    <t>SAO PAULO</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169301290104950</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606911136582536</t>
-  </si>
-  <si>
-    <t>ROMULO FRATINI</t>
-  </si>
-  <si>
-    <t>Avenida Sao Domingos</t>
-  </si>
-  <si>
-    <t>2234</t>
-  </si>
-  <si>
-    <t>Vila Morangueira</t>
-  </si>
-  <si>
-    <t>87040-000</t>
-  </si>
-  <si>
-    <t>Maringa</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606921136598847</t>
-  </si>
-  <si>
-    <t>MARIA DAS GRACAS DA SILVA</t>
-  </si>
-  <si>
-    <t>Rua Desembargador Jose Gomes da Costa</t>
-  </si>
-  <si>
-    <t>1890</t>
-  </si>
-  <si>
-    <t>Capim Macio</t>
-  </si>
-  <si>
-    <t>59082-140</t>
-  </si>
-  <si>
-    <t>Natal</t>
-  </si>
-  <si>
-    <t>RN</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606931136611719</t>
-  </si>
-  <si>
-    <t>MARISA RIBEIRO</t>
-  </si>
-  <si>
-    <t>Rua dos Macunis</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>Vila Madalena</t>
-  </si>
-  <si>
-    <t>05444-001</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169271825808064</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606941136624702</t>
-  </si>
-  <si>
-    <t>ANA BEATRIZ DA SILVA ALVES</t>
-  </si>
-  <si>
-    <t>Rua Marechal Jose Bernardino Bormann</t>
-  </si>
-  <si>
-    <t>1258</t>
-  </si>
-  <si>
-    <t>Bigorrilho</t>
-  </si>
-  <si>
-    <t>80730-350</t>
-  </si>
-  <si>
-    <t>Curitiba</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606951136639510</t>
-  </si>
-  <si>
-    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t>RUA JOAO MOTA</t>
-  </si>
-  <si>
-    <t>471</t>
-  </si>
-  <si>
-    <t>JARDIM DAS PALMEIRAS</t>
-  </si>
-  <si>
-    <t>37538-714</t>
-  </si>
-  <si>
-    <t>Santa Rita do Sapucai</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606961136652930</t>
-  </si>
-  <si>
-    <t>BEATRIZ FIOLA DE LIMA</t>
-  </si>
-  <si>
-    <t>Rua Aurelia</t>
-  </si>
-  <si>
-    <t>1441</t>
-  </si>
-  <si>
-    <t>Vila Romana</t>
-  </si>
-  <si>
-    <t>05046-001</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606971136668612</t>
-  </si>
-  <si>
-    <t>GERUSA TORRES BLANCH</t>
-  </si>
-  <si>
-    <t>Rua Eduardo</t>
-  </si>
-  <si>
-    <t>465</t>
-  </si>
-  <si>
-    <t>Vila Albertina</t>
-  </si>
-  <si>
-    <t>02371-010</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606981136685476</t>
-  </si>
-  <si>
-    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
-  </si>
-  <si>
-    <t>Rua Joao Antonio Biagi</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>Aeroporto</t>
-  </si>
-  <si>
-    <t>14302-126</t>
-  </si>
-  <si>
-    <t>Batatais</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606991136703811</t>
-  </si>
-  <si>
-    <t>GRAZIELLA BARROS</t>
-  </si>
-  <si>
-    <t>Rua Corifeu de Azevedo Marques</t>
-  </si>
-  <si>
-    <t>3213</t>
-  </si>
-  <si>
-    <t>Jardim das Industrias</t>
-  </si>
-  <si>
-    <t>12241-040</t>
-  </si>
-  <si>
-    <t>Sao Jose dos Campos</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607001136723068</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
-  </si>
-  <si>
-    <t>Avenida Engenheiro Alberto De Zagottis</t>
-  </si>
-  <si>
-    <t>1199</t>
-  </si>
-  <si>
-    <t>Jardim Taquaral</t>
-  </si>
-  <si>
-    <t>04675-085</t>
-  </si>
-  <si>
-    <t>35261032014717000189550010000006961933919301</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
-  </si>
-  <si>
-    <t>Rodovia Celso Garcia Cid, km 380</t>
-  </si>
-  <si>
-    <t>S/N</t>
-  </si>
-  <si>
-    <t>Jardim Portal de Versalhes 1</t>
-  </si>
-  <si>
-    <t>86055-900</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169211263927089</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606871103481940</t>
-  </si>
-  <si>
-    <t>APARECIDA</t>
-  </si>
-  <si>
-    <t>Avenida Santos Dumont</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Vila Alzira</t>
-  </si>
-  <si>
-    <t>09015-320</t>
-  </si>
-  <si>
-    <t>Santo Andre</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862130000000000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862140000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862170000000000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169161629085523</t>
-  </si>
-  <si>
-    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169171204845354</t>
-  </si>
-  <si>
-    <t>04571-000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862180000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000004839620000000000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169241326233013</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169251459162513</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169261572131218</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169281477045657</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169291699333540</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169181828741727</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169201210095383</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169221114394191</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000004839890000000000</t>
+    <t>00000000000000000000000000811862190000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862150000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862250000000000</t>
   </si>
   <si>
     <t>35261002648810000184550010001169311529968594</t>
@@ -1762,8 +1816,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1F1F03-088A-4B4B-9AD1-40A4873DB0C0}">
-  <dimension ref="A1:Y57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D103B75-38C8-48F9-B322-9DC3B3FADC94}">
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -1775,6 +1829,7 @@
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="33.88671875" bestFit="1" customWidth="1"/>
@@ -2030,29 +2085,29 @@
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="W6" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -2101,29 +2156,29 @@
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -2172,71 +2227,69 @@
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O9" s="11">
         <v>1</v>
@@ -2245,29 +2298,29 @@
         <v>1</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -2276,13 +2329,13 @@
         <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>42</v>
@@ -2316,29 +2369,29 @@
         <v>1</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -2347,13 +2400,13 @@
         <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>42</v>
@@ -2387,29 +2440,29 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="U11" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="W11" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y11" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="V11" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="W11" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -2418,69 +2471,69 @@
         <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="4" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="O12" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P12" s="11">
         <v>1</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -2489,38 +2542,38 @@
         <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="O13" s="11">
         <v>1</v>
@@ -2529,29 +2582,29 @@
         <v>1</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="V13" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="X13" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="W13" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="Y13" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -2560,38 +2613,38 @@
         <v>29</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="O14" s="11">
         <v>1</v>
@@ -2600,29 +2653,29 @@
         <v>1</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -2631,38 +2684,38 @@
         <v>29</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="O15" s="11">
         <v>1</v>
@@ -2671,71 +2724,71 @@
         <v>1</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="O16" s="11">
         <v>1</v>
@@ -2744,29 +2797,29 @@
         <v>1</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -2775,38 +2828,38 @@
         <v>29</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="O17" s="11">
         <v>1</v>
@@ -2815,71 +2868,69 @@
         <v>1</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>81</v>
-      </c>
+      <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O18" s="11">
         <v>1</v>
@@ -2888,29 +2939,29 @@
         <v>1</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -2919,38 +2970,38 @@
         <v>29</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O19" s="11">
         <v>1</v>
@@ -2959,29 +3010,29 @@
         <v>1</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="W19" s="10" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -2990,38 +3041,38 @@
         <v>29</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="O20" s="11">
         <v>1</v>
@@ -3030,29 +3081,29 @@
         <v>1</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -3061,38 +3112,38 @@
         <v>29</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O21" s="11">
         <v>1</v>
@@ -3101,29 +3152,29 @@
         <v>1</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="R21" s="4"/>
       <c r="S21" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -3132,38 +3183,38 @@
         <v>29</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="4" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="O22" s="11">
         <v>1</v>
@@ -3172,29 +3223,29 @@
         <v>1</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="W22" s="10" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>304</v>
+        <v>238</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
@@ -3203,215 +3254,255 @@
         <v>29</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="4" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="O23" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" s="11">
         <v>1</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="W23" s="10" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
+      <c r="A24" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="4"/>
+      <c r="F24" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K24" s="9"/>
       <c r="L24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="M24" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N24" s="4" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="O24" s="11">
-        <v>6000</v>
+        <v>1</v>
       </c>
       <c r="P24" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>190</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
+      <c r="A25" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="B25" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K25" s="9"/>
       <c r="L25" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M25" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N25" s="4" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="O25" s="11">
-        <v>4098</v>
+        <v>1</v>
       </c>
       <c r="P25" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="W25" s="10" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>190</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="4"/>
+      <c r="G26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K26" s="9"/>
       <c r="L26" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M26" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N26" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="O26" s="11">
         <v>1</v>
@@ -3420,57 +3511,69 @@
         <v>1</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="W26" s="10" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K27" s="9"/>
       <c r="L27" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M27" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N27" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="O27" s="11">
         <v>1</v>
@@ -3479,57 +3582,69 @@
         <v>1</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="V27" s="4" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="W27" s="10" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K28" s="9"/>
       <c r="L28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M28" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N28" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="O28" s="11">
         <v>1</v>
@@ -3538,94 +3653,106 @@
         <v>1</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="V28" s="4" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="W28" s="10" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>212</v>
+        <v>363</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K29" s="9"/>
       <c r="L29" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M29" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N29" s="4" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="O29" s="11">
-        <v>11122</v>
+        <v>1</v>
       </c>
       <c r="P29" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="R29" s="4"/>
       <c r="S29" s="4" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="V29" s="4" t="s">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>316</v>
+        <v>369</v>
       </c>
       <c r="X29" s="4" t="s">
-        <v>317</v>
+        <v>370</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>190</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>106</v>
@@ -3634,66 +3761,78 @@
         <v>31</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="K30" s="9"/>
       <c r="L30" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M30" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N30" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="O30" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" s="11">
         <v>1</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="R30" s="4"/>
       <c r="S30" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="W30" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y30" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="T30" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="U30" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="V30" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="W30" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="Y30" s="4" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="4"/>
@@ -3702,57 +3841,57 @@
       <c r="J31" s="4"/>
       <c r="K31" s="9"/>
       <c r="L31" s="4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="O31" s="11">
-        <v>4</v>
+        <v>11122</v>
       </c>
       <c r="P31" s="11">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="R31" s="4"/>
       <c r="S31" s="4" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="V31" s="4" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="W31" s="10" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="X31" s="4" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>290</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="4"/>
@@ -3761,57 +3900,57 @@
       <c r="J32" s="4"/>
       <c r="K32" s="9"/>
       <c r="L32" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="O32" s="11">
-        <v>1</v>
+        <v>8073</v>
       </c>
       <c r="P32" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="R32" s="4"/>
       <c r="S32" s="4" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="V32" s="4" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="W32" s="10" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>212</v>
+        <v>383</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="4"/>
@@ -3820,57 +3959,57 @@
       <c r="J33" s="4"/>
       <c r="K33" s="9"/>
       <c r="L33" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M33" s="4"/>
       <c r="N33" s="4" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="O33" s="11">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="P33" s="11">
         <v>1</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="R33" s="4"/>
       <c r="S33" s="4" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="V33" s="4" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="W33" s="10" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>212</v>
+        <v>383</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="4"/>
@@ -3879,57 +4018,57 @@
       <c r="J34" s="4"/>
       <c r="K34" s="9"/>
       <c r="L34" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="O34" s="11">
-        <v>1</v>
+        <v>6000</v>
       </c>
       <c r="P34" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="R34" s="4"/>
       <c r="S34" s="4" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="W34" s="10" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="Y34" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="4"/>
@@ -3938,57 +4077,57 @@
       <c r="J35" s="4"/>
       <c r="K35" s="9"/>
       <c r="L35" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O35" s="11">
-        <v>1</v>
+        <v>4098</v>
       </c>
       <c r="P35" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="V35" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="W35" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="4"/>
@@ -3997,57 +4136,57 @@
       <c r="J36" s="4"/>
       <c r="K36" s="9"/>
       <c r="L36" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="O36" s="11">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P36" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="R36" s="4"/>
       <c r="S36" s="4" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="W36" s="10" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="X36" s="4" t="s">
-        <v>212</v>
+        <v>394</v>
       </c>
       <c r="Y36" s="4" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="4"/>
@@ -4056,57 +4195,59 @@
       <c r="J37" s="4"/>
       <c r="K37" s="9"/>
       <c r="L37" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="O37" s="11">
-        <v>12</v>
+        <v>7040</v>
       </c>
       <c r="P37" s="11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="R37" s="4"/>
       <c r="S37" s="4" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="V37" s="4" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="W37" s="10" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="Y37" s="4" t="s">
-        <v>326</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
+      <c r="A38" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="B38" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="4"/>
@@ -4115,57 +4256,47 @@
       <c r="J38" s="4"/>
       <c r="K38" s="9"/>
       <c r="L38" s="4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="O38" s="11">
-        <v>8073</v>
+        <v>300</v>
       </c>
       <c r="P38" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R38" s="4"/>
       <c r="S38" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="T38" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="U38" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="V38" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="W38" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="X38" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y38" s="4" t="s">
-        <v>190</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
+      <c r="A39" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="B39" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="4"/>
@@ -4174,59 +4305,47 @@
       <c r="J39" s="4"/>
       <c r="K39" s="9"/>
       <c r="L39" s="4" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="O39" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P39" s="11">
         <v>1</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="R39" s="4"/>
       <c r="S39" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="T39" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="U39" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="V39" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="W39" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="X39" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="Y39" s="4" t="s">
-        <v>190</v>
-      </c>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="4"/>
@@ -4235,24 +4354,24 @@
       <c r="J40" s="4"/>
       <c r="K40" s="9"/>
       <c r="L40" s="4" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M40" s="4"/>
       <c r="N40" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="O40" s="11">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="P40" s="11">
         <v>1</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="R40" s="4"/>
       <c r="S40" s="4" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
@@ -4262,20 +4381,18 @@
       <c r="Y40" s="4"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="4"/>
@@ -4284,47 +4401,59 @@
       <c r="J41" s="4"/>
       <c r="K41" s="9"/>
       <c r="L41" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="M41" s="4"/>
       <c r="N41" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="O41" s="11">
-        <v>17</v>
+        <v>13107</v>
       </c>
       <c r="P41" s="11">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="R41" s="4"/>
+        <v>400</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>401</v>
+      </c>
       <c r="S41" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="10"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
+        <v>378</v>
+      </c>
+      <c r="T41" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="V41" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="W41" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="X41" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y41" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="4"/>
@@ -4333,45 +4462,61 @@
       <c r="J42" s="4"/>
       <c r="K42" s="9"/>
       <c r="L42" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="M42" s="4"/>
       <c r="N42" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="O42" s="11">
-        <v>4</v>
+        <v>14177</v>
       </c>
       <c r="P42" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="R42" s="4"/>
+        <v>402</v>
+      </c>
+      <c r="R42" s="4" t="s">
+        <v>401</v>
+      </c>
       <c r="S42" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="10"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
+        <v>378</v>
+      </c>
+      <c r="T42" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="V42" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="W42" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="X42" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y42" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
+      <c r="A43" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="B43" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="4"/>
@@ -4380,59 +4525,45 @@
       <c r="J43" s="4"/>
       <c r="K43" s="9"/>
       <c r="L43" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O43" s="11">
-        <v>13107</v>
+        <v>10</v>
       </c>
       <c r="P43" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="R43" s="4" t="s">
-        <v>408</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="R43" s="4"/>
       <c r="S43" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="T43" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="U43" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="V43" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="W43" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="X43" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y43" s="4" t="s">
-        <v>190</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="10"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="4"/>
@@ -4441,61 +4572,57 @@
       <c r="J44" s="4"/>
       <c r="K44" s="9"/>
       <c r="L44" s="4" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="O44" s="11">
-        <v>14177</v>
+        <v>7048</v>
       </c>
       <c r="P44" s="11">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="R44" s="4" t="s">
-        <v>408</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="R44" s="4"/>
       <c r="S44" s="4" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="W44" s="10" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="X44" s="4" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="4"/>
@@ -4504,45 +4631,57 @@
       <c r="J45" s="4"/>
       <c r="K45" s="9"/>
       <c r="L45" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="O45" s="11">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="P45" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="4"/>
-      <c r="Y45" s="4"/>
+        <v>378</v>
+      </c>
+      <c r="T45" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="U45" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="V45" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="W45" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="X45" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y45" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="4"/>
@@ -4551,43 +4690,57 @@
       <c r="J46" s="4"/>
       <c r="K46" s="9"/>
       <c r="L46" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="O46" s="11">
-        <v>4</v>
+        <v>22121</v>
       </c>
       <c r="P46" s="11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
+      <c r="S46" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="T46" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="V46" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="W46" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="X46" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y46" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="4"/>
@@ -4596,57 +4749,57 @@
       <c r="J47" s="4"/>
       <c r="K47" s="9"/>
       <c r="L47" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="O47" s="11">
-        <v>7048</v>
+        <v>61</v>
       </c>
       <c r="P47" s="11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="W47" s="10" t="s">
-        <v>316</v>
+        <v>382</v>
       </c>
       <c r="X47" s="4" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="Y47" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="4"/>
@@ -4655,57 +4808,57 @@
       <c r="J48" s="4"/>
       <c r="K48" s="9"/>
       <c r="L48" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="O48" s="11">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="P48" s="11">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="W48" s="10" t="s">
-        <v>316</v>
+        <v>382</v>
       </c>
       <c r="X48" s="4" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="Y48" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="4"/>
@@ -4714,293 +4867,349 @@
       <c r="J49" s="4"/>
       <c r="K49" s="9"/>
       <c r="L49" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="O49" s="11">
-        <v>22121</v>
+        <v>17122</v>
       </c>
       <c r="P49" s="11">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="W49" s="10" t="s">
-        <v>316</v>
+        <v>382</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="Y49" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>174</v>
+      </c>
       <c r="L50" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="M50" s="4"/>
+        <v>175</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="N50" s="4" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="O50" s="11">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="P50" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4" t="s">
-        <v>312</v>
+        <v>412</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>313</v>
+        <v>413</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>314</v>
+        <v>414</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>315</v>
+        <v>415</v>
       </c>
       <c r="W50" s="10" t="s">
-        <v>316</v>
+        <v>416</v>
       </c>
       <c r="X50" s="4" t="s">
-        <v>317</v>
+        <v>238</v>
       </c>
       <c r="Y50" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="9"/>
+        <v>179</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="L51" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="M51" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="N51" s="4" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="O51" s="11">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="P51" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="4" t="s">
         <v>417</v>
       </c>
       <c r="R51" s="4"/>
       <c r="S51" s="4" t="s">
-        <v>312</v>
+        <v>418</v>
       </c>
       <c r="T51" s="4" t="s">
-        <v>313</v>
+        <v>419</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>314</v>
+        <v>420</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>315</v>
+        <v>421</v>
       </c>
       <c r="W51" s="10" t="s">
-        <v>316</v>
+        <v>422</v>
       </c>
       <c r="X51" s="4" t="s">
-        <v>317</v>
+        <v>423</v>
       </c>
       <c r="Y51" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="9"/>
+        <v>179</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="L52" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="M52" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="N52" s="4" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="O52" s="11">
-        <v>7040</v>
+        <v>1</v>
       </c>
       <c r="P52" s="11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="R52" s="4"/>
       <c r="S52" s="4" t="s">
-        <v>312</v>
+        <v>425</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>313</v>
+        <v>426</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>314</v>
+        <v>427</v>
       </c>
       <c r="V52" s="4" t="s">
-        <v>315</v>
+        <v>428</v>
       </c>
       <c r="W52" s="10" t="s">
-        <v>316</v>
+        <v>429</v>
       </c>
       <c r="X52" s="4" t="s">
-        <v>317</v>
+        <v>430</v>
       </c>
       <c r="Y52" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="9"/>
+        <v>179</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="L53" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="M53" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="N53" s="4" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="O53" s="11">
-        <v>17122</v>
+        <v>1</v>
       </c>
       <c r="P53" s="11">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="R53" s="4"/>
       <c r="S53" s="4" t="s">
-        <v>312</v>
+        <v>432</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>313</v>
+        <v>433</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>314</v>
+        <v>434</v>
       </c>
       <c r="V53" s="4" t="s">
-        <v>315</v>
+        <v>435</v>
       </c>
       <c r="W53" s="10" t="s">
-        <v>316</v>
+        <v>436</v>
       </c>
       <c r="X53" s="4" t="s">
-        <v>317</v>
+        <v>238</v>
       </c>
       <c r="Y53" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="4"/>
@@ -5008,58 +5217,42 @@
       <c r="I54" s="9"/>
       <c r="J54" s="4"/>
       <c r="K54" s="9"/>
-      <c r="L54" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="O54" s="11">
-        <v>3000</v>
+        <v>4</v>
       </c>
       <c r="P54" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="R54" s="4"/>
-      <c r="S54" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="T54" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="U54" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="V54" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="W54" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="X54" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y54" s="4" t="s">
-        <v>190</v>
-      </c>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="4"/>
@@ -5071,13 +5264,13 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="11">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="P55" s="11">
         <v>0</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
@@ -5089,18 +5282,20 @@
       <c r="Y55" s="4"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
+      <c r="A56" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="B56" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="4"/>
@@ -5112,18 +5307,18 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P56" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="R56" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="S56" s="4"/>
+        <v>439</v>
+      </c>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4" t="s">
+        <v>397</v>
+      </c>
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
@@ -5134,16 +5329,16 @@
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="4"/>
@@ -5161,10 +5356,10 @@
         <v>0</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="R57" s="4" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="S57" s="4"/>
       <c r="T57" s="4"/>
@@ -5173,6 +5368,49 @@
       <c r="W57" s="10"/>
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F58" s="9"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="11">
+        <v>0</v>
+      </c>
+      <c r="P58" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="R58" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="10"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/status_saida/operacional/status_out_2026.xlsx
+++ b/data/status_saida/operacional/status_out_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opera\Desktop\app\dashboard_operacao\data\status_saida\operacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{469E7C90-BC58-417E-8074-3B489F043E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BB8FE55-BA2C-41FC-969A-4A36AC4C1BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B293A39-4CF1-4375-A01C-1D3351EF5A67}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F909F3AB-3CDF-4534-91AE-DCEFE5BCEB87}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="468">
   <si>
     <t>Relatório de Pedidos  Geral</t>
   </si>
@@ -158,453 +158,465 @@
     <t>MERCADO LIVRE - CROSS</t>
   </si>
   <si>
+    <t>200001873233408</t>
+  </si>
+  <si>
+    <t>15459</t>
+  </si>
+  <si>
+    <t>RHINO AUTOPARTS DISTRIBUIDORA E IMPORTADORA DE AUTO PEÇAS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:50:08</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:04:56</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:06:03</t>
+  </si>
+  <si>
+    <t>38507</t>
+  </si>
+  <si>
+    <t>26673</t>
+  </si>
+  <si>
     <t>60675</t>
   </si>
   <si>
+    <t>60685</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:48</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:12:54</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:14:25</t>
+  </si>
+  <si>
+    <t>38492</t>
+  </si>
+  <si>
+    <t>26674</t>
+  </si>
+  <si>
+    <t>CORREIOS VETTORE</t>
+  </si>
+  <si>
+    <t>60696</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:37</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:22:46</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:25:13</t>
+  </si>
+  <si>
+    <t>38527</t>
+  </si>
+  <si>
+    <t>60697</t>
+  </si>
+  <si>
+    <t>60698</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:47:44</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:48:36</t>
+  </si>
+  <si>
+    <t>38529</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>60684</t>
+  </si>
+  <si>
+    <t>EM SEPARACAO</t>
+  </si>
+  <si>
+    <t>116930</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:10</t>
+  </si>
+  <si>
+    <t>38525</t>
+  </si>
+  <si>
+    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>116923</t>
+  </si>
+  <si>
+    <t>38522</t>
+  </si>
+  <si>
+    <t>116922</t>
+  </si>
+  <si>
+    <t>38523</t>
+  </si>
+  <si>
+    <t>116921</t>
+  </si>
+  <si>
+    <t>38524</t>
+  </si>
+  <si>
+    <t>116920</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:09</t>
+  </si>
+  <si>
+    <t>38520</t>
+  </si>
+  <si>
+    <t>116918</t>
+  </si>
+  <si>
+    <t>38521</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:40</t>
+  </si>
+  <si>
+    <t>38532</t>
+  </si>
+  <si>
+    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
+  </si>
+  <si>
+    <t>116928</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:46</t>
+  </si>
+  <si>
+    <t>38519</t>
+  </si>
+  <si>
+    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
+  </si>
+  <si>
+    <t>116927</t>
+  </si>
+  <si>
+    <t>38516</t>
+  </si>
+  <si>
+    <t>116929</t>
+  </si>
+  <si>
+    <t>38518</t>
+  </si>
+  <si>
+    <t>116926</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:45</t>
+  </si>
+  <si>
+    <t>38514</t>
+  </si>
+  <si>
+    <t>116925</t>
+  </si>
+  <si>
+    <t>38517</t>
+  </si>
+  <si>
+    <t>116924</t>
+  </si>
+  <si>
+    <t>38515</t>
+  </si>
+  <si>
+    <t>159976</t>
+  </si>
+  <si>
+    <t>81186218</t>
+  </si>
+  <si>
+    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:20:18</t>
+  </si>
+  <si>
+    <t>38513</t>
+  </si>
+  <si>
+    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
+  </si>
+  <si>
+    <t>116917</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:54</t>
+  </si>
+  <si>
+    <t>38509</t>
+  </si>
+  <si>
+    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
+  </si>
+  <si>
+    <t>116916</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:53</t>
+  </si>
+  <si>
+    <t>38508</t>
+  </si>
+  <si>
+    <t>Doação JSA-Zandoná</t>
+  </si>
+  <si>
+    <t>81186217</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:02:42</t>
+  </si>
+  <si>
+    <t>38512</t>
+  </si>
+  <si>
+    <t>02741</t>
+  </si>
+  <si>
+    <t>81186214</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:29:45</t>
+  </si>
+  <si>
+    <t>38510</t>
+  </si>
+  <si>
+    <t>67852</t>
+  </si>
+  <si>
+    <t>81186213</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:50:26</t>
+  </si>
+  <si>
+    <t>38505</t>
+  </si>
+  <si>
+    <t>VENETO</t>
+  </si>
+  <si>
+    <t>EXPEDIDO</t>
+  </si>
+  <si>
+    <t>60694</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:36</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:08:22</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:09:49</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:11:55</t>
+  </si>
+  <si>
+    <t>38526</t>
+  </si>
+  <si>
+    <t>26671</t>
+  </si>
+  <si>
+    <t>JMS CARGO (JADLOG)</t>
+  </si>
+  <si>
     <t>60691</t>
   </si>
   <si>
     <t>01/10/2026 12:02:35</t>
   </si>
   <si>
-    <t>01/10/2026 13:08:22</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:09:49</t>
-  </si>
-  <si>
-    <t>38526</t>
-  </si>
-  <si>
-    <t>26671</t>
-  </si>
-  <si>
-    <t>JMS CARGO (JADLOG)</t>
+    <t>60695</t>
+  </si>
+  <si>
+    <t>60680</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:50:50</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:53:39</t>
+  </si>
+  <si>
+    <t>38494</t>
+  </si>
+  <si>
+    <t>60679</t>
+  </si>
+  <si>
+    <t>60678</t>
+  </si>
+  <si>
+    <t>60699</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:38</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:14:06</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:17:33</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:27:44</t>
+  </si>
+  <si>
+    <t>38530</t>
+  </si>
+  <si>
+    <t>26678</t>
+  </si>
+  <si>
+    <t>SHOPEE EXPRESSS</t>
+  </si>
+  <si>
+    <t>60700</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:31:36</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:33:09</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:15:26</t>
+  </si>
+  <si>
+    <t>38531</t>
+  </si>
+  <si>
+    <t>26677</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - ML FLEX</t>
+  </si>
+  <si>
+    <t>60701</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:39</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:27:03</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:28:24</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:16:14</t>
+  </si>
+  <si>
+    <t>38528</t>
+  </si>
+  <si>
+    <t>26676</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - SHOPEE FLEX</t>
+  </si>
+  <si>
+    <t>60702</t>
+  </si>
+  <si>
+    <t>60703</t>
+  </si>
+  <si>
+    <t>60677</t>
+  </si>
+  <si>
+    <t>60693</t>
   </si>
   <si>
     <t>60692</t>
   </si>
   <si>
-    <t>01/10/2026 12:02:36</t>
-  </si>
-  <si>
-    <t>60693</t>
-  </si>
-  <si>
-    <t>60694</t>
-  </si>
-  <si>
-    <t>60695</t>
-  </si>
-  <si>
-    <t>60696</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:37</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:22:46</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:25:13</t>
-  </si>
-  <si>
-    <t>38527</t>
-  </si>
-  <si>
-    <t>26674</t>
-  </si>
-  <si>
-    <t>CORREIOS VETTORE</t>
-  </si>
-  <si>
-    <t>60697</t>
-  </si>
-  <si>
-    <t>60698</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:47:44</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:48:36</t>
-  </si>
-  <si>
-    <t>38529</t>
-  </si>
-  <si>
-    <t>200001873233408</t>
-  </si>
-  <si>
-    <t>15459</t>
-  </si>
-  <si>
-    <t>RHINO AUTOPARTS DISTRIBUIDORA E IMPORTADORA DE AUTO PEÇAS LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:50:08</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:04:56</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:06:03</t>
-  </si>
-  <si>
-    <t>38507</t>
-  </si>
-  <si>
-    <t>26673</t>
-  </si>
-  <si>
-    <t>60699</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:38</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:14:06</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:17:33</t>
-  </si>
-  <si>
-    <t>38530</t>
-  </si>
-  <si>
-    <t>26678</t>
-  </si>
-  <si>
-    <t>SHOPEE EXPRESSS</t>
+    <t>60681</t>
+  </si>
+  <si>
+    <t>166550891492101</t>
+  </si>
+  <si>
+    <t>60682</t>
+  </si>
+  <si>
+    <t>166546891073601</t>
+  </si>
+  <si>
+    <t>60683</t>
+  </si>
+  <si>
+    <t>60686</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:05:53</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:06:51</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:18:40</t>
+  </si>
+  <si>
+    <t>38491</t>
+  </si>
+  <si>
+    <t>26675</t>
+  </si>
+  <si>
+    <t>TOTAL EXPRESS</t>
+  </si>
+  <si>
+    <t>60687</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:49</t>
+  </si>
+  <si>
+    <t>60688</t>
   </si>
   <si>
     <t>60689</t>
   </si>
   <si>
-    <t>01/10/2026 08:18:49</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:05:53</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:06:51</t>
-  </si>
-  <si>
-    <t>38491</t>
-  </si>
-  <si>
-    <t>26675</t>
-  </si>
-  <si>
-    <t>TOTAL EXPRESS</t>
-  </si>
-  <si>
-    <t>60688</t>
-  </si>
-  <si>
-    <t>60687</t>
-  </si>
-  <si>
-    <t>60686</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:48</t>
-  </si>
-  <si>
-    <t>60685</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:12:54</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:14:25</t>
-  </si>
-  <si>
-    <t>38492</t>
-  </si>
-  <si>
-    <t>60684</t>
-  </si>
-  <si>
-    <t>166546891073601</t>
-  </si>
-  <si>
-    <t>60683</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:50:50</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:53:39</t>
-  </si>
-  <si>
-    <t>38494</t>
-  </si>
-  <si>
-    <t>166550891492101</t>
-  </si>
-  <si>
-    <t>60682</t>
-  </si>
-  <si>
-    <t>60681</t>
-  </si>
-  <si>
-    <t>60680</t>
-  </si>
-  <si>
-    <t>60679</t>
-  </si>
-  <si>
-    <t>60678</t>
-  </si>
-  <si>
-    <t>60677</t>
-  </si>
-  <si>
-    <t>EM SEPARACAO</t>
-  </si>
-  <si>
-    <t>116927</t>
-  </si>
-  <si>
-    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:46</t>
-  </si>
-  <si>
-    <t>38516</t>
-  </si>
-  <si>
-    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
-  </si>
-  <si>
-    <t>116921</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:10</t>
-  </si>
-  <si>
-    <t>38524</t>
-  </si>
-  <si>
-    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>116922</t>
-  </si>
-  <si>
-    <t>38523</t>
-  </si>
-  <si>
-    <t>116923</t>
-  </si>
-  <si>
-    <t>38522</t>
-  </si>
-  <si>
-    <t>116930</t>
-  </si>
-  <si>
-    <t>38525</t>
-  </si>
-  <si>
-    <t>696</t>
-  </si>
-  <si>
-    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:40</t>
-  </si>
-  <si>
-    <t>38532</t>
-  </si>
-  <si>
-    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
-  </si>
-  <si>
-    <t>116918</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:09</t>
-  </si>
-  <si>
-    <t>38521</t>
-  </si>
-  <si>
-    <t>67852</t>
-  </si>
-  <si>
-    <t>81186213</t>
-  </si>
-  <si>
-    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:50:26</t>
-  </si>
-  <si>
-    <t>38505</t>
-  </si>
-  <si>
-    <t>VENETO</t>
-  </si>
-  <si>
-    <t>02741</t>
-  </si>
-  <si>
-    <t>81186214</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:29:45</t>
-  </si>
-  <si>
-    <t>38510</t>
-  </si>
-  <si>
-    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
-  </si>
-  <si>
-    <t>Doação JSA-Zandoná</t>
-  </si>
-  <si>
-    <t>81186217</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:02:42</t>
-  </si>
-  <si>
-    <t>38512</t>
-  </si>
-  <si>
-    <t>116916</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:53</t>
-  </si>
-  <si>
-    <t>38508</t>
-  </si>
-  <si>
-    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
-  </si>
-  <si>
-    <t>116917</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:54</t>
-  </si>
-  <si>
-    <t>38509</t>
-  </si>
-  <si>
-    <t>159976</t>
-  </si>
-  <si>
-    <t>81186218</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:20:18</t>
-  </si>
-  <si>
-    <t>38513</t>
-  </si>
-  <si>
-    <t>116924</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:45</t>
-  </si>
-  <si>
-    <t>38515</t>
-  </si>
-  <si>
-    <t>116925</t>
-  </si>
-  <si>
-    <t>38517</t>
-  </si>
-  <si>
-    <t>116926</t>
-  </si>
-  <si>
-    <t>38514</t>
-  </si>
-  <si>
-    <t>116928</t>
-  </si>
-  <si>
-    <t>38519</t>
-  </si>
-  <si>
-    <t>116929</t>
-  </si>
-  <si>
-    <t>38518</t>
-  </si>
-  <si>
-    <t>116920</t>
-  </si>
-  <si>
-    <t>38520</t>
-  </si>
-  <si>
-    <t>EXPEDIDO</t>
-  </si>
-  <si>
-    <t>60700</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:31:36</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:33:09</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:15:26</t>
-  </si>
-  <si>
-    <t>38531</t>
-  </si>
-  <si>
-    <t>26677</t>
-  </si>
-  <si>
-    <t>TM TRANSPORTE - ML FLEX</t>
-  </si>
-  <si>
-    <t>60701</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:39</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:27:03</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:28:24</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:16:14</t>
-  </si>
-  <si>
-    <t>38528</t>
-  </si>
-  <si>
-    <t>26676</t>
-  </si>
-  <si>
-    <t>TM TRANSPORTE - SHOPEE FLEX</t>
-  </si>
-  <si>
-    <t>60702</t>
-  </si>
-  <si>
-    <t>60703</t>
-  </si>
-  <si>
     <t>PENDENTE</t>
   </si>
   <si>
@@ -614,31 +626,70 @@
     <t>01/10/2026 10:22:35</t>
   </si>
   <si>
+    <t>60704</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:53:50</t>
+  </si>
+  <si>
+    <t>JADLOG LOGISTICA S.A</t>
+  </si>
+  <si>
+    <t>4510105083</t>
+  </si>
+  <si>
+    <t>81186230</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:06:26</t>
+  </si>
+  <si>
+    <t>PED.COT.55569</t>
+  </si>
+  <si>
+    <t>81186225</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:27:32</t>
+  </si>
+  <si>
     <t>81186215</t>
   </si>
   <si>
     <t>01/10/2026 12:09:42</t>
   </si>
   <si>
-    <t>PED.COT.55569</t>
-  </si>
-  <si>
-    <t>81186225</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:27:32</t>
+    <t>CLIENTE RETIRA</t>
   </si>
   <si>
     <t>REJEITADA</t>
   </si>
   <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>8039</t>
+  </si>
+  <si>
+    <t>81186231</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:43:42</t>
+  </si>
+  <si>
     <t>116931</t>
   </si>
   <si>
     <t>01/10/2026 11:32:11</t>
   </si>
   <si>
-    <t>695</t>
+    <t>Whatsapp Paulo Rogério 07/08</t>
+  </si>
+  <si>
+    <t>81186232</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:08:22</t>
   </si>
   <si>
     <t>35261024873172000561550010000606761103412015</t>
@@ -665,6 +716,27 @@
     <t>SP</t>
   </si>
   <si>
+    <t>35261039601246000235550070000154591916765040</t>
+  </si>
+  <si>
+    <t>ADRIANO APARECIDO BELLINI</t>
+  </si>
+  <si>
+    <t>Rua Senador Joaquim Catunda</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Conjunto Habitacional Brigadei</t>
+  </si>
+  <si>
+    <t>04840-300</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
     <t>35261024873172000561550010000606751103406107</t>
   </si>
   <si>
@@ -689,6 +761,213 @@
     <t>PE</t>
   </si>
   <si>
+    <t>35261024873172000561550010000606851103469342</t>
+  </si>
+  <si>
+    <t>ANDREZA CAMELO</t>
+  </si>
+  <si>
+    <t>Avenida Joaquim Lourenco de Toledo Bueno</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Guacuri</t>
+  </si>
+  <si>
+    <t>04475-260</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606961136652930</t>
+  </si>
+  <si>
+    <t>BEATRIZ FIOLA DE LIMA</t>
+  </si>
+  <si>
+    <t>Rua Aurelia</t>
+  </si>
+  <si>
+    <t>1441</t>
+  </si>
+  <si>
+    <t>Vila Romana</t>
+  </si>
+  <si>
+    <t>05046-001</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606971136668612</t>
+  </si>
+  <si>
+    <t>GERUSA TORRES BLANCH</t>
+  </si>
+  <si>
+    <t>Rua Eduardo</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>Vila Albertina</t>
+  </si>
+  <si>
+    <t>02371-010</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606981136685476</t>
+  </si>
+  <si>
+    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
+  </si>
+  <si>
+    <t>Rua Joao Antonio Biagi</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Aeroporto</t>
+  </si>
+  <si>
+    <t>14302-126</t>
+  </si>
+  <si>
+    <t>Batatais</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606841103462472</t>
+  </si>
+  <si>
+    <t>OPERAÇÃO CANCELADA PELO USUÁRIO - Motivo: cancelado pelo cliente</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169301290104950</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
+  </si>
+  <si>
+    <t>RUA SURUBIM</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>CIDADE MONCOES</t>
+  </si>
+  <si>
+    <t>04571-050</t>
+  </si>
+  <si>
+    <t>SAO PAULO</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169231562258086</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169221114394191</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169211263927089</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169201210095383</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169181828741727</t>
+  </si>
+  <si>
+    <t>35261032014717000189550010000006961933919301</t>
+  </si>
+  <si>
+    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
+  </si>
+  <si>
+    <t>Rodovia Celso Garcia Cid, km 380</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>Jardim Portal de Versalhes 1</t>
+  </si>
+  <si>
+    <t>86055-900</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169281477045657</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169271825808064</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169291699333540</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169261572131218</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169251459162513</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169241326233013</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862180000000000</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169171204845354</t>
+  </si>
+  <si>
+    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
+  </si>
+  <si>
+    <t>04571-000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169161629085523</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862170000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862140000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862130000000000</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606941136624702</t>
+  </si>
+  <si>
+    <t>ANA BEATRIZ DA SILVA ALVES</t>
+  </si>
+  <si>
+    <t>Rua Marechal Jose Bernardino Bormann</t>
+  </si>
+  <si>
+    <t>1258</t>
+  </si>
+  <si>
+    <t>Bigorrilho</t>
+  </si>
+  <si>
+    <t>80730-350</t>
+  </si>
+  <si>
+    <t>Curitiba</t>
+  </si>
+  <si>
     <t>35261024873172000561550010000606911136582536</t>
   </si>
   <si>
@@ -710,7 +989,235 @@
     <t>Maringa</t>
   </si>
   <si>
-    <t>PR</t>
+    <t>35261024873172000561550010000606951136639510</t>
+  </si>
+  <si>
+    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t>RUA JOAO MOTA</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>JARDIM DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t>37538-714</t>
+  </si>
+  <si>
+    <t>Santa Rita do Sapucai</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606801103431284</t>
+  </si>
+  <si>
+    <t>GLAUCIA TEREZA BATISTA</t>
+  </si>
+  <si>
+    <t>Rua Jose Ede</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>36200-018</t>
+  </si>
+  <si>
+    <t>Barbacena</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606791103427391</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>Rua Quatorze</t>
+  </si>
+  <si>
+    <t>906</t>
+  </si>
+  <si>
+    <t>Ilha dos Araujos</t>
+  </si>
+  <si>
+    <t>35020-720</t>
+  </si>
+  <si>
+    <t>Governador Valadares</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606781103422546</t>
+  </si>
+  <si>
+    <t>NICOLE BALDO MENDES</t>
+  </si>
+  <si>
+    <t>Rua Maria Manchen de Souza</t>
+  </si>
+  <si>
+    <t>210 apto 1</t>
+  </si>
+  <si>
+    <t>Kobrasol</t>
+  </si>
+  <si>
+    <t>88102-500</t>
+  </si>
+  <si>
+    <t>Sao Jose</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606991136703811</t>
+  </si>
+  <si>
+    <t>GRAZIELLA BARROS</t>
+  </si>
+  <si>
+    <t>Rua Corifeu de Azevedo Marques</t>
+  </si>
+  <si>
+    <t>3213</t>
+  </si>
+  <si>
+    <t>Jardim das Industrias</t>
+  </si>
+  <si>
+    <t>12241-040</t>
+  </si>
+  <si>
+    <t>Sao Jose dos Campos</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607001136723068</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
+  </si>
+  <si>
+    <t>Avenida Engenheiro Alberto De Zagottis</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>Jardim Taquaral</t>
+  </si>
+  <si>
+    <t>04675-085</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607011136737112</t>
+  </si>
+  <si>
+    <t>AMANDA HALEN DE SOUZA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Rua Luiz Scott</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Jardim Iracema/Aldeia</t>
+  </si>
+  <si>
+    <t>06440-260</t>
+  </si>
+  <si>
+    <t>Barueri</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607021136755606</t>
+  </si>
+  <si>
+    <t>LETICIA ARAUJO</t>
+  </si>
+  <si>
+    <t>Rua Serra do Mar</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Tres Montanhas</t>
+  </si>
+  <si>
+    <t>06278-080</t>
+  </si>
+  <si>
+    <t>Osasco</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607031138124805</t>
+  </si>
+  <si>
+    <t>MAIARA FERNANDA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>R Lope de Baena</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Jardim Santa Lucrecia</t>
+  </si>
+  <si>
+    <t>05185-170</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606771103417537</t>
+  </si>
+  <si>
+    <t>NADIA MONTAGNA</t>
+  </si>
+  <si>
+    <t>General Artigas</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Leblon</t>
+  </si>
+  <si>
+    <t>22441-140</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606931136611719</t>
+  </si>
+  <si>
+    <t>MARISA RIBEIRO</t>
+  </si>
+  <si>
+    <t>Rua dos Macunis</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>Vila Madalena</t>
+  </si>
+  <si>
+    <t>05444-001</t>
   </si>
   <si>
     <t>35261024873172000561550010000606921136598847</t>
@@ -737,166 +1244,127 @@
     <t>RN</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606931136611719</t>
-  </si>
-  <si>
-    <t>MARISA RIBEIRO</t>
-  </si>
-  <si>
-    <t>Rua dos Macunis</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>Vila Madalena</t>
-  </si>
-  <si>
-    <t>05444-001</t>
-  </si>
-  <si>
-    <t>Sao Paulo</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606941136624702</t>
-  </si>
-  <si>
-    <t>ANA BEATRIZ DA SILVA ALVES</t>
-  </si>
-  <si>
-    <t>Rua Marechal Jose Bernardino Bormann</t>
-  </si>
-  <si>
-    <t>1258</t>
-  </si>
-  <si>
-    <t>Bigorrilho</t>
-  </si>
-  <si>
-    <t>80730-350</t>
-  </si>
-  <si>
-    <t>Curitiba</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606951136639510</t>
-  </si>
-  <si>
-    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t>RUA JOAO MOTA</t>
-  </si>
-  <si>
-    <t>471</t>
-  </si>
-  <si>
-    <t>JARDIM DAS PALMEIRAS</t>
-  </si>
-  <si>
-    <t>37538-714</t>
-  </si>
-  <si>
-    <t>Santa Rita do Sapucai</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606961136652930</t>
-  </si>
-  <si>
-    <t>BEATRIZ FIOLA DE LIMA</t>
-  </si>
-  <si>
-    <t>Rua Aurelia</t>
-  </si>
-  <si>
-    <t>1441</t>
-  </si>
-  <si>
-    <t>Vila Romana</t>
-  </si>
-  <si>
-    <t>05046-001</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606971136668612</t>
-  </si>
-  <si>
-    <t>GERUSA TORRES BLANCH</t>
-  </si>
-  <si>
-    <t>Rua Eduardo</t>
-  </si>
-  <si>
-    <t>465</t>
-  </si>
-  <si>
-    <t>Vila Albertina</t>
-  </si>
-  <si>
-    <t>02371-010</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606981136685476</t>
-  </si>
-  <si>
-    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
-  </si>
-  <si>
-    <t>Rua Joao Antonio Biagi</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>Aeroporto</t>
-  </si>
-  <si>
-    <t>14302-126</t>
-  </si>
-  <si>
-    <t>Batatais</t>
-  </si>
-  <si>
-    <t>35261039601246000235550070000154591916765040</t>
-  </si>
-  <si>
-    <t>ADRIANO APARECIDO BELLINI</t>
-  </si>
-  <si>
-    <t>Rua Senador Joaquim Catunda</t>
-  </si>
-  <si>
-    <t>077</t>
-  </si>
-  <si>
-    <t>Conjunto Habitacional Brigadei</t>
-  </si>
-  <si>
-    <t>04840-300</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606991136703811</t>
-  </si>
-  <si>
-    <t>GRAZIELLA BARROS</t>
-  </si>
-  <si>
-    <t>Rua Corifeu de Azevedo Marques</t>
-  </si>
-  <si>
-    <t>3213</t>
-  </si>
-  <si>
-    <t>Jardim das Industrias</t>
-  </si>
-  <si>
-    <t>12241-040</t>
-  </si>
-  <si>
-    <t>Sao Jose dos Campos</t>
+    <t>35261024873172000561550010000606811103436097</t>
+  </si>
+  <si>
+    <t>VALERIA ARAUJO</t>
+  </si>
+  <si>
+    <t>SQN 111 Bloco C</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Asa Norte</t>
+  </si>
+  <si>
+    <t>70754-030</t>
+  </si>
+  <si>
+    <t>Brasilia</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606821103440890</t>
+  </si>
+  <si>
+    <t>HERICA SANTOS</t>
+  </si>
+  <si>
+    <t>Rua Messina</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Jardim Carioca</t>
+  </si>
+  <si>
+    <t>21921-360</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606831103451503</t>
+  </si>
+  <si>
+    <t>PAULO VICTOR</t>
+  </si>
+  <si>
+    <t>Quadra QR 323 Conjunto 5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Samambaia Sul</t>
+  </si>
+  <si>
+    <t>72309-605</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606861103474459</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ DE CAMARGO</t>
+  </si>
+  <si>
+    <t>Avenida Sao Paulo</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Jardim Sao Lucas</t>
+  </si>
+  <si>
+    <t>18767-024</t>
+  </si>
+  <si>
+    <t>Cerqueira Cesar</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606871103481940</t>
+  </si>
+  <si>
+    <t>APARECIDA</t>
+  </si>
+  <si>
+    <t>Avenida Santos Dumont</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Vila Alzira</t>
+  </si>
+  <si>
+    <t>09015-320</t>
+  </si>
+  <si>
+    <t>Santo Andre</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606881103488098</t>
+  </si>
+  <si>
+    <t>GUILHERME VINICIUS</t>
+  </si>
+  <si>
+    <t>Rua Luis Carlos Simonini</t>
+  </si>
+  <si>
+    <t>Mundo</t>
+  </si>
+  <si>
+    <t>Jardim Paraiso</t>
+  </si>
+  <si>
+    <t>18558-052</t>
+  </si>
+  <si>
+    <t>Boituva</t>
   </si>
   <si>
     <t>35261024873172000561550010000606891103494885</t>
@@ -920,457 +1388,61 @@
     <t>Palhoca</t>
   </si>
   <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606881103488098</t>
-  </si>
-  <si>
-    <t>GUILHERME VINICIUS</t>
-  </si>
-  <si>
-    <t>Rua Luis Carlos Simonini</t>
-  </si>
-  <si>
-    <t>Mundo</t>
-  </si>
-  <si>
-    <t>Jardim Paraiso</t>
-  </si>
-  <si>
-    <t>18558-052</t>
-  </si>
-  <si>
-    <t>Boituva</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606871103481940</t>
-  </si>
-  <si>
-    <t>APARECIDA</t>
-  </si>
-  <si>
-    <t>Avenida Santos Dumont</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Vila Alzira</t>
-  </si>
-  <si>
-    <t>09015-320</t>
-  </si>
-  <si>
-    <t>Santo Andre</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606861103474459</t>
-  </si>
-  <si>
-    <t>ANDRE LUIZ DE CAMARGO</t>
-  </si>
-  <si>
-    <t>Avenida Sao Paulo</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Jardim Sao Lucas</t>
-  </si>
-  <si>
-    <t>18767-024</t>
-  </si>
-  <si>
-    <t>Cerqueira Cesar</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606851103469342</t>
-  </si>
-  <si>
-    <t>ANDREZA CAMELO</t>
-  </si>
-  <si>
-    <t>Avenida Joaquim Lourenco de Toledo Bueno</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Guacuri</t>
-  </si>
-  <si>
-    <t>04475-260</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606841103462472</t>
+    <t>00000000000000000000000000811862190000000000</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607041153406619</t>
   </si>
   <si>
     <t>ANA PAULA BENTO GALLO</t>
   </si>
   <si>
-    <t>Rua America</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Atibaia jardim</t>
-  </si>
-  <si>
-    <t>12942-170</t>
+    <t>Rua Padre Feliciano Grande</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>Alvinopolis</t>
+  </si>
+  <si>
+    <t>12942-460</t>
   </si>
   <si>
     <t>Atibaia</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606831103451503</t>
-  </si>
-  <si>
-    <t>PAULO VICTOR</t>
-  </si>
-  <si>
-    <t>Quadra QR 323 Conjunto 5</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Samambaia Sul</t>
-  </si>
-  <si>
-    <t>72309-605</t>
-  </si>
-  <si>
-    <t>Brasilia</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606821103440890</t>
-  </si>
-  <si>
-    <t>HERICA SANTOS</t>
-  </si>
-  <si>
-    <t>Rua Messina</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Jardim Carioca</t>
-  </si>
-  <si>
-    <t>21921-360</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606811103436097</t>
-  </si>
-  <si>
-    <t>VALERIA ARAUJO</t>
-  </si>
-  <si>
-    <t>SQN 111 Bloco C</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Asa Norte</t>
-  </si>
-  <si>
-    <t>70754-030</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606801103431284</t>
-  </si>
-  <si>
-    <t>GLAUCIA TEREZA BATISTA</t>
-  </si>
-  <si>
-    <t>Rua Jose Ede</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>36200-018</t>
-  </si>
-  <si>
-    <t>Barbacena</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606791103427391</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>Rua Quatorze</t>
-  </si>
-  <si>
-    <t>906</t>
-  </si>
-  <si>
-    <t>Ilha dos Araujos</t>
-  </si>
-  <si>
-    <t>35020-720</t>
-  </si>
-  <si>
-    <t>Governador Valadares</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606781103422546</t>
-  </si>
-  <si>
-    <t>NICOLE BALDO MENDES</t>
-  </si>
-  <si>
-    <t>Rua Maria Manchen de Souza</t>
-  </si>
-  <si>
-    <t>210 apto 1</t>
-  </si>
-  <si>
-    <t>Kobrasol</t>
-  </si>
-  <si>
-    <t>88102-500</t>
-  </si>
-  <si>
-    <t>Sao Jose</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606771103417537</t>
-  </si>
-  <si>
-    <t>NADIA MONTAGNA</t>
-  </si>
-  <si>
-    <t>General Artigas</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Leblon</t>
-  </si>
-  <si>
-    <t>22441-140</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169271825808064</t>
-  </si>
-  <si>
-    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
-  </si>
-  <si>
-    <t>RUA SURUBIM</t>
-  </si>
-  <si>
-    <t>577</t>
-  </si>
-  <si>
-    <t>CIDADE MONCOES</t>
-  </si>
-  <si>
-    <t>04571-050</t>
-  </si>
-  <si>
-    <t>SAO PAULO</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169211263927089</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169221114394191</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169231562258086</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169301290104950</t>
-  </si>
-  <si>
-    <t>35261032014717000189550010000006961933919301</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
-  </si>
-  <si>
-    <t>Rodovia Celso Garcia Cid, km 380</t>
-  </si>
-  <si>
-    <t>S/N</t>
-  </si>
-  <si>
-    <t>Jardim Portal de Versalhes 1</t>
-  </si>
-  <si>
-    <t>86055-900</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169181828741727</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862130000000000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862140000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862170000000000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169161629085523</t>
-  </si>
-  <si>
-    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169171204845354</t>
-  </si>
-  <si>
-    <t>04571-000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862180000000000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169241326233013</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169251459162513</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169261572131218</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169281477045657</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169291699333540</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169201210095383</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607001136723068</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
-  </si>
-  <si>
-    <t>Avenida Engenheiro Alberto De Zagottis</t>
-  </si>
-  <si>
-    <t>1199</t>
-  </si>
-  <si>
-    <t>Jardim Taquaral</t>
-  </si>
-  <si>
-    <t>04675-085</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607011136737112</t>
-  </si>
-  <si>
-    <t>AMANDA HALEN DE SOUZA NOGUEIRA</t>
-  </si>
-  <si>
-    <t>Rua Luiz Scott</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Jardim Iracema/Aldeia</t>
-  </si>
-  <si>
-    <t>06440-260</t>
-  </si>
-  <si>
-    <t>Barueri</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607021136755606</t>
-  </si>
-  <si>
-    <t>LETICIA ARAUJO</t>
-  </si>
-  <si>
-    <t>Rua Serra do Mar</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>Tres Montanhas</t>
-  </si>
-  <si>
-    <t>06278-080</t>
-  </si>
-  <si>
-    <t>Osasco</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607031138124805</t>
-  </si>
-  <si>
-    <t>MAIARA FERNANDA SILVA LIMA</t>
-  </si>
-  <si>
-    <t>R Lope de Baena</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>Jardim Santa Lucrecia</t>
-  </si>
-  <si>
-    <t>05185-170</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862190000000000</t>
+    <t>00000000000000000000000000811862300000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862250000000000</t>
   </si>
   <si>
     <t>00000000000000000000000000811862150000000000</t>
   </si>
   <si>
-    <t>00000000000000000000000000811862250000000000</t>
+    <t>35261032014717000189550010000006951807549676</t>
+  </si>
+  <si>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: CRN 003 - DMSO 50 ml - VALIDADE: 01/10/2026 14:54:00. Qtde. Sol.: 12  Qtde. Disp.: 0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862310000000000</t>
+  </si>
+  <si>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000220820170 - DW-DS-625-M18-120 Det. Prox. - VALIDADE: 01/10/2026 14:43:50. Qtde. Sol.: 2  Qtde. Disp.: 0</t>
   </si>
   <si>
     <t>35261002648810000184550010001169311529968594</t>
   </si>
   <si>
-    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: PEM000002 - SACO 100 MOEDAS - PEBD - LISO - VALIDADE: 01/10/2026 11:32:21. Qtde. Sol.: 1000  Qtde. Disp.: 0</t>
-  </si>
-  <si>
-    <t>35261032014717000189550010000006951807549676</t>
-  </si>
-  <si>
-    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: CRN 003 - DMSO 50 ml - VALIDADE: 01/10/2026 12:02:54. Qtde. Sol.: 12  Qtde. Disp.: 0</t>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: PEM000002 - SACO 100 MOEDAS - PEBD - LISO - VALIDADE: 01/10/2026 14:54:00. Qtde. Sol.: 1000  Qtde. Disp.: 0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862320000000000</t>
+  </si>
+  <si>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000220220773 - DW-HD-603-M18-411 Det. Prox. - VALIDADE: 01/10/2026 15:08:29. Qtde. Sol.: 2  Qtde. Disp.: 0</t>
   </si>
 </sst>
 </file>
@@ -1816,11 +1888,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D103B75-38C8-48F9-B322-9DC3B3FADC94}">
-  <dimension ref="A1:Y58"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7522A01F-5450-474A-9B37-7FD19851779C}">
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="78.44140625" bestFit="1" customWidth="1"/>
@@ -1836,7 +1908,7 @@
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="130.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="134.109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="45.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -2085,66 +2157,68 @@
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="W6" s="10" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>38</v>
@@ -2156,29 +2230,29 @@
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -2187,38 +2261,38 @@
         <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O8" s="11">
         <v>1</v>
@@ -2227,29 +2301,29 @@
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -2258,38 +2332,38 @@
         <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="O9" s="11">
         <v>1</v>
@@ -2298,29 +2372,29 @@
         <v>1</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -2329,38 +2403,38 @@
         <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="O10" s="11">
         <v>1</v>
@@ -2369,29 +2443,29 @@
         <v>1</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -2400,38 +2474,38 @@
         <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="O11" s="11">
         <v>1</v>
@@ -2440,29 +2514,29 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -2471,1368 +2545,1116 @@
         <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="4" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O12" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P12" s="11">
         <v>1</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
       <c r="O13" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="W13" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>207</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="4"/>
       <c r="K14" s="9"/>
       <c r="L14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="O14" s="11">
-        <v>1</v>
+        <v>4098</v>
       </c>
       <c r="P14" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="9"/>
       <c r="L15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>37</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="O15" s="11">
-        <v>1</v>
+        <v>6000</v>
       </c>
       <c r="P15" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="4"/>
       <c r="K16" s="9"/>
       <c r="L16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>71</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="O16" s="11">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="P16" s="11">
         <v>1</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="9"/>
       <c r="L17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="O17" s="11">
-        <v>1</v>
+        <v>8073</v>
       </c>
       <c r="P17" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="4"/>
       <c r="K18" s="9"/>
       <c r="L18" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="O18" s="11">
-        <v>1</v>
+        <v>17122</v>
       </c>
       <c r="P18" s="11">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="9"/>
       <c r="L19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>84</v>
-      </c>
+      <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="O19" s="11">
-        <v>1</v>
+        <v>7040</v>
       </c>
       <c r="P19" s="11">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="W19" s="10" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="9"/>
       <c r="L20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="O20" s="11">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="4"/>
       <c r="K21" s="9"/>
       <c r="L21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O21" s="11">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="P21" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="R21" s="4"/>
       <c r="S21" s="4" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="O22" s="11">
-        <v>1</v>
+        <v>11122</v>
       </c>
       <c r="P22" s="11">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="W22" s="10" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="9"/>
       <c r="L23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="O23" s="11">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="P23" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="W23" s="10" t="s">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>95</v>
-      </c>
+      <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="4"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="O24" s="11">
-        <v>1</v>
+        <v>22121</v>
       </c>
       <c r="P24" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4" t="s">
-        <v>329</v>
+        <v>268</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>331</v>
+        <v>270</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>332</v>
+        <v>271</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>333</v>
+        <v>272</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>334</v>
+        <v>273</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>335</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="M25" s="4"/>
       <c r="N25" s="4" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="O25" s="11">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="P25" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
-        <v>337</v>
+        <v>268</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>339</v>
+        <v>270</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>340</v>
+        <v>271</v>
       </c>
       <c r="W25" s="10" t="s">
-        <v>341</v>
+        <v>272</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>342</v>
+        <v>273</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>343</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="4"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="O26" s="11">
-        <v>1</v>
+        <v>7048</v>
       </c>
       <c r="P26" s="11">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>344</v>
+        <v>292</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>345</v>
+        <v>268</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>346</v>
+        <v>269</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="W26" s="10" t="s">
-        <v>349</v>
+        <v>272</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>334</v>
+        <v>273</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>335</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
+      <c r="A27" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="O27" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P27" s="11">
         <v>1</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="T27" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="U27" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="V27" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="W27" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="X27" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="Y27" s="4" t="s">
-        <v>253</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="O28" s="11">
-        <v>1</v>
+        <v>14177</v>
       </c>
       <c r="P28" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="R28" s="4"/>
+        <v>295</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="S28" s="4" t="s">
-        <v>358</v>
+        <v>268</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>359</v>
+        <v>269</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="V28" s="4" t="s">
-        <v>361</v>
+        <v>271</v>
       </c>
       <c r="W28" s="10" t="s">
-        <v>362</v>
+        <v>297</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>363</v>
+        <v>273</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="4"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="O29" s="11">
-        <v>1</v>
+        <v>13107</v>
       </c>
       <c r="P29" s="11">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="R29" s="4"/>
+        <v>298</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="S29" s="4" t="s">
-        <v>365</v>
+        <v>268</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>366</v>
+        <v>269</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>367</v>
+        <v>270</v>
       </c>
       <c r="V29" s="4" t="s">
-        <v>368</v>
+        <v>271</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>369</v>
+        <v>272</v>
       </c>
       <c r="X29" s="4" t="s">
-        <v>370</v>
+        <v>273</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
+      <c r="A30" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="B30" s="4" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E30" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="9"/>
       <c r="L30" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="M30" s="4"/>
       <c r="N30" s="4" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="O30" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P30" s="11">
         <v>1</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="R30" s="4"/>
       <c r="S30" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="T30" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="U30" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="V30" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="W30" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y30" s="4" t="s">
-        <v>343</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
+      <c r="A31" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="B31" s="4" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="4"/>
@@ -3841,57 +3663,47 @@
       <c r="J31" s="4"/>
       <c r="K31" s="9"/>
       <c r="L31" s="4" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O31" s="11">
-        <v>11122</v>
+        <v>17</v>
       </c>
       <c r="P31" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>377</v>
+        <v>300</v>
       </c>
       <c r="R31" s="4"/>
       <c r="S31" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="T31" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="U31" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="V31" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="W31" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="X31" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y31" s="4" t="s">
-        <v>207</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="B32" s="4" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="4"/>
@@ -3900,1124 +3712,1390 @@
       <c r="J32" s="4"/>
       <c r="K32" s="9"/>
       <c r="L32" s="4" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O32" s="11">
-        <v>8073</v>
+        <v>300</v>
       </c>
       <c r="P32" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="R32" s="4"/>
       <c r="S32" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="T32" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="U32" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="V32" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="W32" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="X32" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y32" s="4" t="s">
-        <v>207</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L33" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="M33" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N33" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="O33" s="11">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="P33" s="11">
         <v>1</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="R33" s="4"/>
       <c r="S33" s="4" t="s">
-        <v>378</v>
+        <v>303</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>379</v>
+        <v>304</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>380</v>
+        <v>305</v>
       </c>
       <c r="V33" s="4" t="s">
-        <v>381</v>
+        <v>306</v>
       </c>
       <c r="W33" s="10" t="s">
-        <v>382</v>
+        <v>307</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>383</v>
+        <v>308</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L34" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="M34" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N34" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="O34" s="11">
-        <v>6000</v>
+        <v>1</v>
       </c>
       <c r="P34" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="R34" s="4"/>
       <c r="S34" s="4" t="s">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>380</v>
+        <v>312</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>381</v>
+        <v>313</v>
       </c>
       <c r="W34" s="10" t="s">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>383</v>
+        <v>315</v>
       </c>
       <c r="Y34" s="4" t="s">
-        <v>207</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="M35" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N35" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="O35" s="11">
-        <v>4098</v>
+        <v>4</v>
       </c>
       <c r="P35" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>387</v>
+        <v>316</v>
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4" t="s">
-        <v>378</v>
+        <v>317</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>379</v>
+        <v>318</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>380</v>
+        <v>319</v>
       </c>
       <c r="V35" s="4" t="s">
-        <v>381</v>
+        <v>320</v>
       </c>
       <c r="W35" s="10" t="s">
-        <v>382</v>
+        <v>321</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>383</v>
+        <v>322</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>207</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L36" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="M36" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N36" s="4" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="O36" s="11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P36" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="R36" s="4"/>
       <c r="S36" s="4" t="s">
-        <v>389</v>
+        <v>325</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>390</v>
+        <v>326</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>392</v>
+        <v>328</v>
       </c>
       <c r="W36" s="10" t="s">
-        <v>393</v>
+        <v>329</v>
       </c>
       <c r="X36" s="4" t="s">
-        <v>394</v>
+        <v>330</v>
       </c>
       <c r="Y36" s="4" t="s">
-        <v>223</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L37" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="M37" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N37" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="O37" s="11">
-        <v>7040</v>
+        <v>1</v>
       </c>
       <c r="P37" s="11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>395</v>
+        <v>331</v>
       </c>
       <c r="R37" s="4"/>
       <c r="S37" s="4" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="V37" s="4" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="W37" s="10" t="s">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="Y37" s="4" t="s">
-        <v>207</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L38" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M38" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N38" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O38" s="11">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="P38" s="11">
         <v>1</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>396</v>
+        <v>338</v>
       </c>
       <c r="R38" s="4"/>
       <c r="S38" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
+        <v>339</v>
+      </c>
+      <c r="T38" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="V38" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="W38" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="X38" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y38" s="4" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="9"/>
+        <v>149</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>152</v>
+      </c>
       <c r="L39" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="M39" s="4"/>
+        <v>153</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="N39" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O39" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P39" s="11">
         <v>1</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="R39" s="4"/>
       <c r="S39" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="10"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
+        <v>347</v>
+      </c>
+      <c r="T39" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="V39" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="W39" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="X39" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y39" s="4" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>142</v>
-      </c>
+      <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="9"/>
+        <v>149</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>159</v>
+      </c>
       <c r="L40" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="M40" s="4"/>
+        <v>160</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="N40" s="4" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="O40" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P40" s="11">
         <v>1</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>399</v>
+        <v>353</v>
       </c>
       <c r="R40" s="4"/>
       <c r="S40" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
+        <v>354</v>
+      </c>
+      <c r="T40" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="V40" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="W40" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="X40" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y40" s="4" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="9"/>
+        <v>164</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>167</v>
+      </c>
       <c r="L41" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="M41" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="N41" s="4" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="O41" s="11">
-        <v>13107</v>
+        <v>1</v>
       </c>
       <c r="P41" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>401</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="R41" s="4"/>
       <c r="S41" s="4" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="T41" s="4" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="V41" s="4" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="W41" s="10" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="X41" s="4" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="Y41" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="9"/>
+        <v>164</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>167</v>
+      </c>
       <c r="L42" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M42" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="N42" s="4" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="O42" s="11">
-        <v>14177</v>
+        <v>1</v>
       </c>
       <c r="P42" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="R42" s="4" t="s">
-        <v>401</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="R42" s="4"/>
       <c r="S42" s="4" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="W42" s="10" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="Y42" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="9"/>
+        <v>164</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>167</v>
+      </c>
       <c r="L43" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="M43" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="N43" s="4" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="O43" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P43" s="11">
         <v>1</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
+        <v>374</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="W43" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="X43" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y43" s="4" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L44" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="M44" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N44" s="4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="O44" s="11">
-        <v>7048</v>
+        <v>2</v>
       </c>
       <c r="P44" s="11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="R44" s="4"/>
       <c r="S44" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="W44" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="X44" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>207</v>
+        <v>386</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L45" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="M45" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N45" s="4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="O45" s="11">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="P45" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="W45" s="10" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="X45" s="4" t="s">
-        <v>383</v>
+        <v>231</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L46" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="M46" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N46" s="4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="O46" s="11">
-        <v>22121</v>
+        <v>1</v>
       </c>
       <c r="P46" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="R46" s="4"/>
       <c r="S46" s="4" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="W46" s="10" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="X46" s="4" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="Y46" s="4" t="s">
-        <v>207</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L47" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="M47" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N47" s="4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="O47" s="11">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="P47" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="W47" s="10" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="X47" s="4" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="Y47" s="4" t="s">
-        <v>207</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
+      <c r="A48" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="B48" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" s="9"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L48" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="M48" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N48" s="4" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="O48" s="11">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="P48" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="4" t="s">
         <v>409</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="W48" s="10" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="X48" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Y48" s="4" t="s">
-        <v>207</v>
+        <v>386</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
+      <c r="A49" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="B49" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="L49" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="M49" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="N49" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="O49" s="11">
-        <v>17122</v>
+        <v>1</v>
       </c>
       <c r="P49" s="11">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="W49" s="10" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="Y49" s="4" t="s">
-        <v>207</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="O50" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50" s="11">
         <v>1</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="W50" s="10" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="X50" s="4" t="s">
-        <v>238</v>
+        <v>427</v>
       </c>
       <c r="Y50" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="O51" s="11">
         <v>1</v>
@@ -5026,71 +5104,71 @@
         <v>1</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="R51" s="4"/>
       <c r="S51" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="T51" s="4" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="W51" s="10" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="X51" s="4" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="Y51" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O52" s="11">
         <v>1</v>
@@ -5099,71 +5177,71 @@
         <v>1</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="R52" s="4"/>
       <c r="S52" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="V52" s="4" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="W52" s="10" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="X52" s="4" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="Y52" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O53" s="11">
         <v>1</v>
@@ -5172,44 +5250,44 @@
         <v>1</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="R53" s="4"/>
       <c r="S53" s="4" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="V53" s="4" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="W53" s="10" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="X53" s="4" t="s">
-        <v>238</v>
+        <v>448</v>
       </c>
       <c r="Y53" s="4" t="s">
-        <v>207</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="4"/>
@@ -5220,16 +5298,16 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="O54" s="11">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P54" s="11">
         <v>0</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="R54" s="4"/>
       <c r="S54" s="4"/>
@@ -5243,16 +5321,16 @@
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="4"/>
@@ -5262,40 +5340,56 @@
       <c r="K55" s="9"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
+      <c r="N55" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="O55" s="11">
-        <v>307</v>
+        <v>1</v>
       </c>
       <c r="P55" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="10"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
+      <c r="S55" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="T55" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="U55" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="V55" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="W55" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="X55" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="Y55" s="4" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="4"/>
@@ -5307,17 +5401,17 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="11">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P56" s="11">
         <v>1</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="R56" s="4"/>
       <c r="S56" s="4" t="s">
-        <v>397</v>
+        <v>294</v>
       </c>
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
@@ -5327,18 +5421,20 @@
       <c r="Y56" s="4"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
+      <c r="A57" s="4" t="s">
+        <v>201</v>
+      </c>
       <c r="B57" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="4"/>
@@ -5350,18 +5446,18 @@
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P57" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="R57" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="S57" s="4"/>
+        <v>458</v>
+      </c>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4" t="s">
+        <v>294</v>
+      </c>
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
@@ -5372,16 +5468,16 @@
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="4"/>
@@ -5391,19 +5487,19 @@
       <c r="K58" s="9"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
+      <c r="N58" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="O58" s="11">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="P58" s="11">
         <v>0</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="R58" s="4" t="s">
-        <v>443</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
@@ -5411,6 +5507,182 @@
       <c r="W58" s="10"/>
       <c r="X58" s="4"/>
       <c r="Y58" s="4"/>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" s="9"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="11">
+        <v>0</v>
+      </c>
+      <c r="P59" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="R59" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="10"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="9"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="11">
+        <v>0</v>
+      </c>
+      <c r="P60" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="R60" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="10"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="11">
+        <v>0</v>
+      </c>
+      <c r="P61" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="R61" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="10"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="11">
+        <v>0</v>
+      </c>
+      <c r="P62" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="R62" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/data/status_saida/operacional/status_out_2026.xlsx
+++ b/data/status_saida/operacional/status_out_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opera\Desktop\app\dashboard_operacao\data\status_saida\operacional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BB8FE55-BA2C-41FC-969A-4A36AC4C1BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{739D7299-558B-4054-AA7A-51DAC86FA9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F909F3AB-3CDF-4534-91AE-DCEFE5BCEB87}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{578A4D5D-6B8E-4E1D-8A6A-BF0F374D0BB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="491">
   <si>
     <t>Relatório de Pedidos  Geral</t>
   </si>
@@ -158,6 +158,9 @@
     <t>MERCADO LIVRE - CROSS</t>
   </si>
   <si>
+    <t>60675</t>
+  </si>
+  <si>
     <t>200001873233408</t>
   </si>
   <si>
@@ -182,21 +185,402 @@
     <t>26673</t>
   </si>
   <si>
-    <t>60675</t>
+    <t>60698</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:37</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:47:44</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:48:36</t>
+  </si>
+  <si>
+    <t>38529</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>60684</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:48</t>
+  </si>
+  <si>
+    <t>EM SEPARACAO</t>
+  </si>
+  <si>
+    <t>116927</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:46</t>
+  </si>
+  <si>
+    <t>38516</t>
+  </si>
+  <si>
+    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
+  </si>
+  <si>
+    <t>116921</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:10</t>
+  </si>
+  <si>
+    <t>38524</t>
+  </si>
+  <si>
+    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
+  </si>
+  <si>
+    <t>116928</t>
+  </si>
+  <si>
+    <t>38519</t>
+  </si>
+  <si>
+    <t>116929</t>
+  </si>
+  <si>
+    <t>38518</t>
+  </si>
+  <si>
+    <t>116918</t>
+  </si>
+  <si>
+    <t>01/10/2026 11:32:09</t>
+  </si>
+  <si>
+    <t>38521</t>
+  </si>
+  <si>
+    <t>116920</t>
+  </si>
+  <si>
+    <t>38520</t>
+  </si>
+  <si>
+    <t>116922</t>
+  </si>
+  <si>
+    <t>38523</t>
+  </si>
+  <si>
+    <t>116923</t>
+  </si>
+  <si>
+    <t>38522</t>
+  </si>
+  <si>
+    <t>116930</t>
+  </si>
+  <si>
+    <t>38525</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:40</t>
+  </si>
+  <si>
+    <t>38532</t>
+  </si>
+  <si>
+    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
+  </si>
+  <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>38534</t>
+  </si>
+  <si>
+    <t>PED.COT.55569</t>
+  </si>
+  <si>
+    <t>81186225</t>
+  </si>
+  <si>
+    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:27:32</t>
+  </si>
+  <si>
+    <t>38537</t>
+  </si>
+  <si>
+    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
+  </si>
+  <si>
+    <t>4510105083</t>
+  </si>
+  <si>
+    <t>81186230</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:06:26</t>
+  </si>
+  <si>
+    <t>38538</t>
+  </si>
+  <si>
+    <t>60704</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:53:50</t>
+  </si>
+  <si>
+    <t>38535</t>
+  </si>
+  <si>
+    <t>JMS CARGO (JADLOG)</t>
+  </si>
+  <si>
+    <t>Whatsapp Paulo Rogério 07/08</t>
+  </si>
+  <si>
+    <t>81186232</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:08:22</t>
+  </si>
+  <si>
+    <t>38539</t>
+  </si>
+  <si>
+    <t>483993</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:46:41</t>
+  </si>
+  <si>
+    <t>38533</t>
+  </si>
+  <si>
+    <t>483994</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:58:37</t>
+  </si>
+  <si>
+    <t>38536</t>
+  </si>
+  <si>
+    <t>CLIENTE RETIRA</t>
+  </si>
+  <si>
+    <t>4503397667</t>
+  </si>
+  <si>
+    <t>81186234</t>
+  </si>
+  <si>
+    <t>01/10/2026 16:27:04</t>
+  </si>
+  <si>
+    <t>38540</t>
+  </si>
+  <si>
+    <t>LEMA TRANSPORTES</t>
+  </si>
+  <si>
+    <t>483997</t>
+  </si>
+  <si>
+    <t>01/10/2026 16:28:38</t>
+  </si>
+  <si>
+    <t>116925</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:31:45</t>
+  </si>
+  <si>
+    <t>38517</t>
+  </si>
+  <si>
+    <t>116924</t>
+  </si>
+  <si>
+    <t>38515</t>
+  </si>
+  <si>
+    <t>159976</t>
+  </si>
+  <si>
+    <t>81186218</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:20:18</t>
+  </si>
+  <si>
+    <t>38513</t>
+  </si>
+  <si>
+    <t>116917</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:54</t>
+  </si>
+  <si>
+    <t>38509</t>
+  </si>
+  <si>
+    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
+  </si>
+  <si>
+    <t>116916</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:09:53</t>
+  </si>
+  <si>
+    <t>38508</t>
+  </si>
+  <si>
+    <t>Doação JSA-Zandoná</t>
+  </si>
+  <si>
+    <t>81186217</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:02:42</t>
+  </si>
+  <si>
+    <t>38512</t>
+  </si>
+  <si>
+    <t>02741</t>
+  </si>
+  <si>
+    <t>81186214</t>
+  </si>
+  <si>
+    <t>01/10/2026 09:29:45</t>
+  </si>
+  <si>
+    <t>38510</t>
+  </si>
+  <si>
+    <t>67852</t>
+  </si>
+  <si>
+    <t>81186213</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:50:26</t>
+  </si>
+  <si>
+    <t>38505</t>
+  </si>
+  <si>
+    <t>VENETO</t>
+  </si>
+  <si>
+    <t>116926</t>
+  </si>
+  <si>
+    <t>38514</t>
+  </si>
+  <si>
+    <t>EXPEDIDO</t>
+  </si>
+  <si>
+    <t>60702</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:39</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:27:03</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:28:24</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:16:14</t>
+  </si>
+  <si>
+    <t>38528</t>
+  </si>
+  <si>
+    <t>26676</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - SHOPEE FLEX</t>
+  </si>
+  <si>
+    <t>60688</t>
+  </si>
+  <si>
+    <t>01/10/2026 08:18:49</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:05:53</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:06:51</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:18:40</t>
+  </si>
+  <si>
+    <t>38491</t>
+  </si>
+  <si>
+    <t>26675</t>
+  </si>
+  <si>
+    <t>TOTAL EXPRESS</t>
+  </si>
+  <si>
+    <t>60703</t>
+  </si>
+  <si>
+    <t>60687</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:08:22</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:09:49</t>
+  </si>
+  <si>
+    <t>01/10/2026 14:11:55</t>
+  </si>
+  <si>
+    <t>38526</t>
+  </si>
+  <si>
+    <t>26671</t>
+  </si>
+  <si>
+    <t>60686</t>
   </si>
   <si>
     <t>60685</t>
   </si>
   <si>
-    <t>01/10/2026 08:18:48</t>
-  </si>
-  <si>
     <t>01/10/2026 11:12:54</t>
   </si>
   <si>
     <t>01/10/2026 11:14:25</t>
   </si>
   <si>
+    <t>01/10/2026 15:54:28</t>
+  </si>
+  <si>
     <t>38492</t>
   </si>
   <si>
@@ -206,256 +590,118 @@
     <t>CORREIOS VETTORE</t>
   </si>
   <si>
+    <t>166546891073601</t>
+  </si>
+  <si>
+    <t>60683</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:50:50</t>
+  </si>
+  <si>
+    <t>01/10/2026 10:53:39</t>
+  </si>
+  <si>
+    <t>38494</t>
+  </si>
+  <si>
+    <t>166550891492101</t>
+  </si>
+  <si>
+    <t>60682</t>
+  </si>
+  <si>
+    <t>60681</t>
+  </si>
+  <si>
+    <t>60680</t>
+  </si>
+  <si>
+    <t>60679</t>
+  </si>
+  <si>
+    <t>60678</t>
+  </si>
+  <si>
+    <t>60677</t>
+  </si>
+  <si>
+    <t>60701</t>
+  </si>
+  <si>
+    <t>60700</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:38</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:31:36</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:33:09</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:15:26</t>
+  </si>
+  <si>
+    <t>38531</t>
+  </si>
+  <si>
+    <t>26677</t>
+  </si>
+  <si>
+    <t>TM TRANSPORTE - ML FLEX</t>
+  </si>
+  <si>
+    <t>60699</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:14:06</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:17:33</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:27:44</t>
+  </si>
+  <si>
+    <t>38530</t>
+  </si>
+  <si>
+    <t>26678</t>
+  </si>
+  <si>
+    <t>SHOPEE EXPRESSS</t>
+  </si>
+  <si>
+    <t>60697</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:22:46</t>
+  </si>
+  <si>
+    <t>01/10/2026 13:25:13</t>
+  </si>
+  <si>
+    <t>38527</t>
+  </si>
+  <si>
     <t>60696</t>
   </si>
   <si>
-    <t>01/10/2026 12:02:37</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:22:46</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:25:13</t>
-  </si>
-  <si>
-    <t>38527</t>
-  </si>
-  <si>
-    <t>60697</t>
-  </si>
-  <si>
-    <t>60698</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:47:44</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:48:36</t>
-  </si>
-  <si>
-    <t>38529</t>
-  </si>
-  <si>
-    <t>CANCELADA</t>
-  </si>
-  <si>
-    <t>60684</t>
-  </si>
-  <si>
-    <t>EM SEPARACAO</t>
-  </si>
-  <si>
-    <t>116930</t>
-  </si>
-  <si>
-    <t>GIESECKE+DEVRIENT CURRENCY TECHNOLOGY BRASIL SERVICOS E COMERCIO DE SOLUCOES TECNOLOGICAS LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:10</t>
-  </si>
-  <si>
-    <t>38525</t>
-  </si>
-  <si>
-    <t>NEXUS LOGISTICA E TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>116923</t>
-  </si>
-  <si>
-    <t>38522</t>
-  </si>
-  <si>
-    <t>116922</t>
-  </si>
-  <si>
-    <t>38523</t>
-  </si>
-  <si>
-    <t>116921</t>
-  </si>
-  <si>
-    <t>38524</t>
-  </si>
-  <si>
-    <t>116920</t>
-  </si>
-  <si>
-    <t>01/10/2026 11:32:09</t>
-  </si>
-  <si>
-    <t>38520</t>
-  </si>
-  <si>
-    <t>116918</t>
-  </si>
-  <si>
-    <t>38521</t>
-  </si>
-  <si>
-    <t>696</t>
-  </si>
-  <si>
-    <t>BIOHEALTH COMERCIO E IMPORTACAO DE EQUIPAMENTOS E PRODUTOS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:40</t>
-  </si>
-  <si>
-    <t>38532</t>
-  </si>
-  <si>
-    <t>UNICARGO TRANSPORTES E CARGAS LTDA</t>
-  </si>
-  <si>
-    <t>116928</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:46</t>
-  </si>
-  <si>
-    <t>38519</t>
-  </si>
-  <si>
-    <t>BRINGER DO BRASIL AGENCIAMENTO DE CARGAS</t>
-  </si>
-  <si>
-    <t>116927</t>
-  </si>
-  <si>
-    <t>38516</t>
-  </si>
-  <si>
-    <t>116929</t>
-  </si>
-  <si>
-    <t>38518</t>
-  </si>
-  <si>
-    <t>116926</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:31:45</t>
-  </si>
-  <si>
-    <t>38514</t>
-  </si>
-  <si>
-    <t>116925</t>
-  </si>
-  <si>
-    <t>38517</t>
-  </si>
-  <si>
-    <t>116924</t>
-  </si>
-  <si>
-    <t>38515</t>
-  </si>
-  <si>
-    <t>159976</t>
-  </si>
-  <si>
-    <t>81186218</t>
-  </si>
-  <si>
-    <t>CONTRINEX PRODUÇÃO DE SISTEMAS DEAUTOMAÇÃO LTDA.</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:20:18</t>
-  </si>
-  <si>
-    <t>38513</t>
-  </si>
-  <si>
-    <t>EMPRESA BRASILEIRA DE CORREIOS</t>
-  </si>
-  <si>
-    <t>116917</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:54</t>
-  </si>
-  <si>
-    <t>38509</t>
-  </si>
-  <si>
-    <t>DEXALOG SOLUCOES LOGISTICAS LTDA</t>
-  </si>
-  <si>
-    <t>116916</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:09:53</t>
-  </si>
-  <si>
-    <t>38508</t>
-  </si>
-  <si>
-    <t>Doação JSA-Zandoná</t>
-  </si>
-  <si>
-    <t>81186217</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:02:42</t>
-  </si>
-  <si>
-    <t>38512</t>
-  </si>
-  <si>
-    <t>02741</t>
-  </si>
-  <si>
-    <t>81186214</t>
-  </si>
-  <si>
-    <t>01/10/2026 09:29:45</t>
-  </si>
-  <si>
-    <t>38510</t>
-  </si>
-  <si>
-    <t>67852</t>
-  </si>
-  <si>
-    <t>81186213</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:50:26</t>
-  </si>
-  <si>
-    <t>38505</t>
-  </si>
-  <si>
-    <t>VENETO</t>
-  </si>
-  <si>
-    <t>EXPEDIDO</t>
+    <t>60695</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:02:36</t>
   </si>
   <si>
     <t>60694</t>
   </si>
   <si>
-    <t>01/10/2026 12:02:36</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:08:22</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:09:49</t>
-  </si>
-  <si>
-    <t>01/10/2026 14:11:55</t>
-  </si>
-  <si>
-    <t>38526</t>
-  </si>
-  <si>
-    <t>26671</t>
-  </si>
-  <si>
-    <t>JMS CARGO (JADLOG)</t>
+    <t>60693</t>
+  </si>
+  <si>
+    <t>60692</t>
   </si>
   <si>
     <t>60691</t>
@@ -464,232 +710,43 @@
     <t>01/10/2026 12:02:35</t>
   </si>
   <si>
-    <t>60695</t>
-  </si>
-  <si>
-    <t>60680</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:50:50</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:53:39</t>
-  </si>
-  <si>
-    <t>38494</t>
-  </si>
-  <si>
-    <t>60679</t>
-  </si>
-  <si>
-    <t>60678</t>
-  </si>
-  <si>
-    <t>60699</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:38</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:14:06</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:17:33</t>
-  </si>
-  <si>
-    <t>01/10/2026 15:27:44</t>
-  </si>
-  <si>
-    <t>38530</t>
-  </si>
-  <si>
-    <t>26678</t>
-  </si>
-  <si>
-    <t>SHOPEE EXPRESSS</t>
-  </si>
-  <si>
-    <t>60700</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:31:36</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:33:09</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:15:26</t>
-  </si>
-  <si>
-    <t>38531</t>
-  </si>
-  <si>
-    <t>26677</t>
-  </si>
-  <si>
-    <t>TM TRANSPORTE - ML FLEX</t>
-  </si>
-  <si>
-    <t>60701</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:02:39</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:27:03</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:28:24</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:16:14</t>
-  </si>
-  <si>
-    <t>38528</t>
-  </si>
-  <si>
-    <t>26676</t>
-  </si>
-  <si>
-    <t>TM TRANSPORTE - SHOPEE FLEX</t>
-  </si>
-  <si>
-    <t>60702</t>
-  </si>
-  <si>
-    <t>60703</t>
-  </si>
-  <si>
-    <t>60677</t>
-  </si>
-  <si>
-    <t>60693</t>
-  </si>
-  <si>
-    <t>60692</t>
-  </si>
-  <si>
-    <t>60681</t>
-  </si>
-  <si>
-    <t>166550891492101</t>
-  </si>
-  <si>
-    <t>60682</t>
-  </si>
-  <si>
-    <t>166546891073601</t>
-  </si>
-  <si>
-    <t>60683</t>
-  </si>
-  <si>
-    <t>60686</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:05:53</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:06:51</t>
-  </si>
-  <si>
-    <t>01/10/2026 14:18:40</t>
-  </si>
-  <si>
-    <t>38491</t>
-  </si>
-  <si>
-    <t>26675</t>
-  </si>
-  <si>
-    <t>TOTAL EXPRESS</t>
-  </si>
-  <si>
-    <t>60687</t>
-  </si>
-  <si>
-    <t>01/10/2026 08:18:49</t>
-  </si>
-  <si>
-    <t>60688</t>
-  </si>
-  <si>
     <t>60689</t>
   </si>
   <si>
-    <t>PENDENTE</t>
-  </si>
-  <si>
-    <t>81186219</t>
-  </si>
-  <si>
-    <t>01/10/2026 10:22:35</t>
-  </si>
-  <si>
-    <t>60704</t>
-  </si>
-  <si>
-    <t>01/10/2026 14:53:50</t>
-  </si>
-  <si>
-    <t>JADLOG LOGISTICA S.A</t>
-  </si>
-  <si>
-    <t>4510105083</t>
-  </si>
-  <si>
-    <t>81186230</t>
-  </si>
-  <si>
-    <t>01/10/2026 14:06:26</t>
-  </si>
-  <si>
-    <t>PED.COT.55569</t>
-  </si>
-  <si>
-    <t>81186225</t>
-  </si>
-  <si>
-    <t>01/10/2026 13:27:32</t>
-  </si>
-  <si>
-    <t>81186215</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:09:42</t>
-  </si>
-  <si>
-    <t>CLIENTE RETIRA</t>
+    <t>8039</t>
   </si>
   <si>
     <t>REJEITADA</t>
   </si>
   <si>
-    <t>695</t>
-  </si>
-  <si>
-    <t>8039</t>
-  </si>
-  <si>
     <t>81186231</t>
   </si>
   <si>
     <t>01/10/2026 14:43:42</t>
   </si>
   <si>
+    <t>PED.COT.075045</t>
+  </si>
+  <si>
+    <t>81186233</t>
+  </si>
+  <si>
+    <t>01/10/2026 15:54:09</t>
+  </si>
+  <si>
     <t>116931</t>
   </si>
   <si>
     <t>01/10/2026 11:32:11</t>
   </si>
   <si>
-    <t>Whatsapp Paulo Rogério 07/08</t>
-  </si>
-  <si>
-    <t>81186232</t>
-  </si>
-  <si>
-    <t>01/10/2026 15:08:22</t>
+    <t>PED.EMAIL</t>
+  </si>
+  <si>
+    <t>81186235</t>
+  </si>
+  <si>
+    <t>01/10/2026 16:35:31</t>
   </si>
   <si>
     <t>35261024873172000561550010000606761103412015</t>
@@ -716,6 +773,30 @@
     <t>SP</t>
   </si>
   <si>
+    <t>35261024873172000561550010000606751103406107</t>
+  </si>
+  <si>
+    <t>WILLIANE ARRUDA SCHIESARO (AW20250627053803)</t>
+  </si>
+  <si>
+    <t>Rua Prefeito Luis De Magalhaes</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>Peixinhos</t>
+  </si>
+  <si>
+    <t>53300-050</t>
+  </si>
+  <si>
+    <t>Olinda</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
     <t>35261039601246000235550070000154591916765040</t>
   </si>
   <si>
@@ -737,28 +818,283 @@
     <t>Sao Paulo</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606751103406107</t>
-  </si>
-  <si>
-    <t>WILLIANE ARRUDA SCHIESARO (AW20250627053803)</t>
-  </si>
-  <si>
-    <t>Rua Prefeito Luis De Magalhaes</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>Peixinhos</t>
-  </si>
-  <si>
-    <t>53300-050</t>
-  </si>
-  <si>
-    <t>Olinda</t>
-  </si>
-  <si>
-    <t>PE</t>
+    <t>35261024873172000561550010000606981136685476</t>
+  </si>
+  <si>
+    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
+  </si>
+  <si>
+    <t>Rua Joao Antonio Biagi</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Aeroporto</t>
+  </si>
+  <si>
+    <t>14302-126</t>
+  </si>
+  <si>
+    <t>Batatais</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606841103462472</t>
+  </si>
+  <si>
+    <t>OPERAÇÃO CANCELADA PELO USUÁRIO - Motivo: cancelado pelo cliente</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169271825808064</t>
+  </si>
+  <si>
+    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
+  </si>
+  <si>
+    <t>RUA SURUBIM</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>CIDADE MONCOES</t>
+  </si>
+  <si>
+    <t>04571-050</t>
+  </si>
+  <si>
+    <t>SAO PAULO</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169211263927089</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169281477045657</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169291699333540</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169181828741727</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169201210095383</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169221114394191</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169231562258086</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169301290104950</t>
+  </si>
+  <si>
+    <t>35261032014717000189550010000006961933919301</t>
+  </si>
+  <si>
+    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
+  </si>
+  <si>
+    <t>Rodovia Celso Garcia Cid, km 380</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>Jardim Portal de Versalhes 1</t>
+  </si>
+  <si>
+    <t>86055-900</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>35261032014717000189550010000006951807549676</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862250000000000</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862300000000000</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607041153406619</t>
+  </si>
+  <si>
+    <t>ANA PAULA BENTO GALLO</t>
+  </si>
+  <si>
+    <t>Rua Padre Feliciano Grande</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>Alvinopolis</t>
+  </si>
+  <si>
+    <t>12942-460</t>
+  </si>
+  <si>
+    <t>Atibaia</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862320000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000004839930000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000004839940000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862340000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000004839970000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169251459162513</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169241326233013</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862180000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169171204845354</t>
+  </si>
+  <si>
+    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
+  </si>
+  <si>
+    <t>04571-000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169161629085523</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862170000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862140000000000</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862130000000000</t>
+  </si>
+  <si>
+    <t>35261002648810000184550010001169261572131218</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607021136755606</t>
+  </si>
+  <si>
+    <t>LETICIA ARAUJO</t>
+  </si>
+  <si>
+    <t>Rua Serra do Mar</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Tres Montanhas</t>
+  </si>
+  <si>
+    <t>06278-080</t>
+  </si>
+  <si>
+    <t>Osasco</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606881103488098</t>
+  </si>
+  <si>
+    <t>GUILHERME VINICIUS</t>
+  </si>
+  <si>
+    <t>Rua Luis Carlos Simonini</t>
+  </si>
+  <si>
+    <t>Mundo</t>
+  </si>
+  <si>
+    <t>Jardim Paraiso</t>
+  </si>
+  <si>
+    <t>18558-052</t>
+  </si>
+  <si>
+    <t>Boituva</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607031138124805</t>
+  </si>
+  <si>
+    <t>MAIARA FERNANDA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>R Lope de Baena</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Jardim Santa Lucrecia</t>
+  </si>
+  <si>
+    <t>05185-170</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606871103481940</t>
+  </si>
+  <si>
+    <t>APARECIDA</t>
+  </si>
+  <si>
+    <t>Avenida Santos Dumont</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Vila Alzira</t>
+  </si>
+  <si>
+    <t>09015-320</t>
+  </si>
+  <si>
+    <t>Santo Andre</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606861103474459</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ DE CAMARGO</t>
+  </si>
+  <si>
+    <t>Avenida Sao Paulo</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Jardim Sao Lucas</t>
+  </si>
+  <si>
+    <t>18767-024</t>
+  </si>
+  <si>
+    <t>Cerqueira Cesar</t>
   </si>
   <si>
     <t>35261024873172000561550010000606851103469342</t>
@@ -779,6 +1115,237 @@
     <t>04475-260</t>
   </si>
   <si>
+    <t>35261024873172000561550010000606831103451503</t>
+  </si>
+  <si>
+    <t>PAULO VICTOR</t>
+  </si>
+  <si>
+    <t>Quadra QR 323 Conjunto 5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Samambaia Sul</t>
+  </si>
+  <si>
+    <t>72309-605</t>
+  </si>
+  <si>
+    <t>Brasilia</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606821103440890</t>
+  </si>
+  <si>
+    <t>HERICA SANTOS</t>
+  </si>
+  <si>
+    <t>Rua Messina</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Jardim Carioca</t>
+  </si>
+  <si>
+    <t>21921-360</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606811103436097</t>
+  </si>
+  <si>
+    <t>VALERIA ARAUJO</t>
+  </si>
+  <si>
+    <t>SQN 111 Bloco C</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Asa Norte</t>
+  </si>
+  <si>
+    <t>70754-030</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606801103431284</t>
+  </si>
+  <si>
+    <t>GLAUCIA TEREZA BATISTA</t>
+  </si>
+  <si>
+    <t>Rua Jose Ede</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>36200-018</t>
+  </si>
+  <si>
+    <t>Barbacena</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606791103427391</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>Rua Quatorze</t>
+  </si>
+  <si>
+    <t>906</t>
+  </si>
+  <si>
+    <t>Ilha dos Araujos</t>
+  </si>
+  <si>
+    <t>35020-720</t>
+  </si>
+  <si>
+    <t>Governador Valadares</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606781103422546</t>
+  </si>
+  <si>
+    <t>NICOLE BALDO MENDES</t>
+  </si>
+  <si>
+    <t>Rua Maria Manchen de Souza</t>
+  </si>
+  <si>
+    <t>210 apto 1</t>
+  </si>
+  <si>
+    <t>Kobrasol</t>
+  </si>
+  <si>
+    <t>88102-500</t>
+  </si>
+  <si>
+    <t>Sao Jose</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606771103417537</t>
+  </si>
+  <si>
+    <t>NADIA MONTAGNA</t>
+  </si>
+  <si>
+    <t>General Artigas</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Leblon</t>
+  </si>
+  <si>
+    <t>22441-140</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607011136737112</t>
+  </si>
+  <si>
+    <t>AMANDA HALEN DE SOUZA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Rua Luiz Scott</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Jardim Iracema/Aldeia</t>
+  </si>
+  <si>
+    <t>06440-260</t>
+  </si>
+  <si>
+    <t>Barueri</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000607001136723068</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
+  </si>
+  <si>
+    <t>Avenida Engenheiro Alberto De Zagottis</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>Jardim Taquaral</t>
+  </si>
+  <si>
+    <t>04675-085</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606991136703811</t>
+  </si>
+  <si>
+    <t>GRAZIELLA BARROS</t>
+  </si>
+  <si>
+    <t>Rua Corifeu de Azevedo Marques</t>
+  </si>
+  <si>
+    <t>3213</t>
+  </si>
+  <si>
+    <t>Jardim das Industrias</t>
+  </si>
+  <si>
+    <t>12241-040</t>
+  </si>
+  <si>
+    <t>Sao Jose dos Campos</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606971136668612</t>
+  </si>
+  <si>
+    <t>GERUSA TORRES BLANCH</t>
+  </si>
+  <si>
+    <t>Rua Eduardo</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>Vila Albertina</t>
+  </si>
+  <si>
+    <t>02371-010</t>
+  </si>
+  <si>
     <t>35261024873172000561550010000606961136652930</t>
   </si>
   <si>
@@ -797,154 +1364,25 @@
     <t>05046-001</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606971136668612</t>
-  </si>
-  <si>
-    <t>GERUSA TORRES BLANCH</t>
-  </si>
-  <si>
-    <t>Rua Eduardo</t>
-  </si>
-  <si>
-    <t>465</t>
-  </si>
-  <si>
-    <t>Vila Albertina</t>
-  </si>
-  <si>
-    <t>02371-010</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606981136685476</t>
-  </si>
-  <si>
-    <t>ANGELA JULIANA DOS SANTOS PEREIRA (ANGELAPEREIRAPEREIRA)</t>
-  </si>
-  <si>
-    <t>Rua Joao Antonio Biagi</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>Aeroporto</t>
-  </si>
-  <si>
-    <t>14302-126</t>
-  </si>
-  <si>
-    <t>Batatais</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606841103462472</t>
-  </si>
-  <si>
-    <t>OPERAÇÃO CANCELADA PELO USUÁRIO - Motivo: cancelado pelo cliente</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169301290104950</t>
-  </si>
-  <si>
-    <t>GIESECKE+DEVRIENT CT BRASIL SERV E COM DE SOL TEC LTDA</t>
-  </si>
-  <si>
-    <t>RUA SURUBIM</t>
-  </si>
-  <si>
-    <t>577</t>
-  </si>
-  <si>
-    <t>CIDADE MONCOES</t>
-  </si>
-  <si>
-    <t>04571-050</t>
-  </si>
-  <si>
-    <t>SAO PAULO</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169231562258086</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169221114394191</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169211263927089</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169201210095383</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169181828741727</t>
-  </si>
-  <si>
-    <t>35261032014717000189550010000006961933919301</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE LONDRINA</t>
-  </si>
-  <si>
-    <t>Rodovia Celso Garcia Cid, km 380</t>
-  </si>
-  <si>
-    <t>S/N</t>
-  </si>
-  <si>
-    <t>Jardim Portal de Versalhes 1</t>
-  </si>
-  <si>
-    <t>86055-900</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169281477045657</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169271825808064</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169291699333540</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169261572131218</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169251459162513</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169241326233013</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862180000000000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169171204845354</t>
-  </si>
-  <si>
-    <t>Foi identificado uma duplicidade interna, por gentileza informe o suporte.</t>
-  </si>
-  <si>
-    <t>04571-000</t>
-  </si>
-  <si>
-    <t>35261002648810000184550010001169161629085523</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862170000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862140000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862130000000000</t>
+    <t>35261024873172000561550010000606951136639510</t>
+  </si>
+  <si>
+    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t>RUA JOAO MOTA</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>JARDIM DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t>37538-714</t>
+  </si>
+  <si>
+    <t>Santa Rita do Sapucai</t>
   </si>
   <si>
     <t>35261024873172000561550010000606941136624702</t>
@@ -968,6 +1406,48 @@
     <t>Curitiba</t>
   </si>
   <si>
+    <t>35261024873172000561550010000606931136611719</t>
+  </si>
+  <si>
+    <t>MARISA RIBEIRO</t>
+  </si>
+  <si>
+    <t>Rua dos Macunis</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>Vila Madalena</t>
+  </si>
+  <si>
+    <t>05444-001</t>
+  </si>
+  <si>
+    <t>35261024873172000561550010000606921136598847</t>
+  </si>
+  <si>
+    <t>MARIA DAS GRACAS DA SILVA</t>
+  </si>
+  <si>
+    <t>Rua Desembargador Jose Gomes da Costa</t>
+  </si>
+  <si>
+    <t>1890</t>
+  </si>
+  <si>
+    <t>Capim Macio</t>
+  </si>
+  <si>
+    <t>59082-140</t>
+  </si>
+  <si>
+    <t>Natal</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
     <t>35261024873172000561550010000606911136582536</t>
   </si>
   <si>
@@ -989,384 +1469,6 @@
     <t>Maringa</t>
   </si>
   <si>
-    <t>35261024873172000561550010000606951136639510</t>
-  </si>
-  <si>
-    <t>JFL EQUIPAMENTOS ELETRONICOS INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t>RUA JOAO MOTA</t>
-  </si>
-  <si>
-    <t>471</t>
-  </si>
-  <si>
-    <t>JARDIM DAS PALMEIRAS</t>
-  </si>
-  <si>
-    <t>37538-714</t>
-  </si>
-  <si>
-    <t>Santa Rita do Sapucai</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606801103431284</t>
-  </si>
-  <si>
-    <t>GLAUCIA TEREZA BATISTA</t>
-  </si>
-  <si>
-    <t>Rua Jose Ede</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>36200-018</t>
-  </si>
-  <si>
-    <t>Barbacena</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606791103427391</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>Rua Quatorze</t>
-  </si>
-  <si>
-    <t>906</t>
-  </si>
-  <si>
-    <t>Ilha dos Araujos</t>
-  </si>
-  <si>
-    <t>35020-720</t>
-  </si>
-  <si>
-    <t>Governador Valadares</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606781103422546</t>
-  </si>
-  <si>
-    <t>NICOLE BALDO MENDES</t>
-  </si>
-  <si>
-    <t>Rua Maria Manchen de Souza</t>
-  </si>
-  <si>
-    <t>210 apto 1</t>
-  </si>
-  <si>
-    <t>Kobrasol</t>
-  </si>
-  <si>
-    <t>88102-500</t>
-  </si>
-  <si>
-    <t>Sao Jose</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606991136703811</t>
-  </si>
-  <si>
-    <t>GRAZIELLA BARROS</t>
-  </si>
-  <si>
-    <t>Rua Corifeu de Azevedo Marques</t>
-  </si>
-  <si>
-    <t>3213</t>
-  </si>
-  <si>
-    <t>Jardim das Industrias</t>
-  </si>
-  <si>
-    <t>12241-040</t>
-  </si>
-  <si>
-    <t>Sao Jose dos Campos</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607001136723068</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO BLEY (MARCO.BLEY)</t>
-  </si>
-  <si>
-    <t>Avenida Engenheiro Alberto De Zagottis</t>
-  </si>
-  <si>
-    <t>1199</t>
-  </si>
-  <si>
-    <t>Jardim Taquaral</t>
-  </si>
-  <si>
-    <t>04675-085</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607011136737112</t>
-  </si>
-  <si>
-    <t>AMANDA HALEN DE SOUZA NOGUEIRA</t>
-  </si>
-  <si>
-    <t>Rua Luiz Scott</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Jardim Iracema/Aldeia</t>
-  </si>
-  <si>
-    <t>06440-260</t>
-  </si>
-  <si>
-    <t>Barueri</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607021136755606</t>
-  </si>
-  <si>
-    <t>LETICIA ARAUJO</t>
-  </si>
-  <si>
-    <t>Rua Serra do Mar</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>Tres Montanhas</t>
-  </si>
-  <si>
-    <t>06278-080</t>
-  </si>
-  <si>
-    <t>Osasco</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607031138124805</t>
-  </si>
-  <si>
-    <t>MAIARA FERNANDA SILVA LIMA</t>
-  </si>
-  <si>
-    <t>R Lope de Baena</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>Jardim Santa Lucrecia</t>
-  </si>
-  <si>
-    <t>05185-170</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606771103417537</t>
-  </si>
-  <si>
-    <t>NADIA MONTAGNA</t>
-  </si>
-  <si>
-    <t>General Artigas</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Leblon</t>
-  </si>
-  <si>
-    <t>22441-140</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606931136611719</t>
-  </si>
-  <si>
-    <t>MARISA RIBEIRO</t>
-  </si>
-  <si>
-    <t>Rua dos Macunis</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>Vila Madalena</t>
-  </si>
-  <si>
-    <t>05444-001</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606921136598847</t>
-  </si>
-  <si>
-    <t>MARIA DAS GRACAS DA SILVA</t>
-  </si>
-  <si>
-    <t>Rua Desembargador Jose Gomes da Costa</t>
-  </si>
-  <si>
-    <t>1890</t>
-  </si>
-  <si>
-    <t>Capim Macio</t>
-  </si>
-  <si>
-    <t>59082-140</t>
-  </si>
-  <si>
-    <t>Natal</t>
-  </si>
-  <si>
-    <t>RN</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606811103436097</t>
-  </si>
-  <si>
-    <t>VALERIA ARAUJO</t>
-  </si>
-  <si>
-    <t>SQN 111 Bloco C</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Asa Norte</t>
-  </si>
-  <si>
-    <t>70754-030</t>
-  </si>
-  <si>
-    <t>Brasilia</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606821103440890</t>
-  </si>
-  <si>
-    <t>HERICA SANTOS</t>
-  </si>
-  <si>
-    <t>Rua Messina</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Jardim Carioca</t>
-  </si>
-  <si>
-    <t>21921-360</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606831103451503</t>
-  </si>
-  <si>
-    <t>PAULO VICTOR</t>
-  </si>
-  <si>
-    <t>Quadra QR 323 Conjunto 5</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Samambaia Sul</t>
-  </si>
-  <si>
-    <t>72309-605</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606861103474459</t>
-  </si>
-  <si>
-    <t>ANDRE LUIZ DE CAMARGO</t>
-  </si>
-  <si>
-    <t>Avenida Sao Paulo</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Jardim Sao Lucas</t>
-  </si>
-  <si>
-    <t>18767-024</t>
-  </si>
-  <si>
-    <t>Cerqueira Cesar</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606871103481940</t>
-  </si>
-  <si>
-    <t>APARECIDA</t>
-  </si>
-  <si>
-    <t>Avenida Santos Dumont</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Vila Alzira</t>
-  </si>
-  <si>
-    <t>09015-320</t>
-  </si>
-  <si>
-    <t>Santo Andre</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000606881103488098</t>
-  </si>
-  <si>
-    <t>GUILHERME VINICIUS</t>
-  </si>
-  <si>
-    <t>Rua Luis Carlos Simonini</t>
-  </si>
-  <si>
-    <t>Mundo</t>
-  </si>
-  <si>
-    <t>Jardim Paraiso</t>
-  </si>
-  <si>
-    <t>18558-052</t>
-  </si>
-  <si>
-    <t>Boituva</t>
-  </si>
-  <si>
     <t>35261024873172000561550010000606891103494885</t>
   </si>
   <si>
@@ -1388,61 +1490,28 @@
     <t>Palhoca</t>
   </si>
   <si>
-    <t>00000000000000000000000000811862190000000000</t>
-  </si>
-  <si>
-    <t>35261024873172000561550010000607041153406619</t>
-  </si>
-  <si>
-    <t>ANA PAULA BENTO GALLO</t>
-  </si>
-  <si>
-    <t>Rua Padre Feliciano Grande</t>
-  </si>
-  <si>
-    <t>492</t>
-  </si>
-  <si>
-    <t>Alvinopolis</t>
-  </si>
-  <si>
-    <t>12942-460</t>
-  </si>
-  <si>
-    <t>Atibaia</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862300000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862250000000000</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862150000000000</t>
-  </si>
-  <si>
-    <t>35261032014717000189550010000006951807549676</t>
-  </si>
-  <si>
-    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: CRN 003 - DMSO 50 ml - VALIDADE: 01/10/2026 14:54:00. Qtde. Sol.: 12  Qtde. Disp.: 0</t>
-  </si>
-  <si>
     <t>00000000000000000000000000811862310000000000</t>
   </si>
   <si>
-    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000220820170 - DW-DS-625-M18-120 Det. Prox. - VALIDADE: 01/10/2026 14:43:50. Qtde. Sol.: 2  Qtde. Disp.: 0</t>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000220820170 - DW-DS-625-M18-120 Det. Prox. - VALIDADE: 01/10/2026 16:33:59. Qtde. Sol.: 2  Qtde. Disp.: 0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862330000000000</t>
+  </si>
+  <si>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000605002386 - S12-4FUG-050 Conec.c/cabo - VALIDADE: 01/10/2026 15:54:16. Qtde. Sol.: 2  Qtde. Disp.: 0</t>
   </si>
   <si>
     <t>35261002648810000184550010001169311529968594</t>
   </si>
   <si>
-    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: PEM000002 - SACO 100 MOEDAS - PEBD - LISO - VALIDADE: 01/10/2026 14:54:00. Qtde. Sol.: 1000  Qtde. Disp.: 0</t>
-  </si>
-  <si>
-    <t>00000000000000000000000000811862320000000000</t>
-  </si>
-  <si>
-    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000220220773 - DW-HD-603-M18-411 Det. Prox. - VALIDADE: 01/10/2026 15:08:29. Qtde. Sol.: 2  Qtde. Disp.: 0</t>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: PEM000002 - SACO 100 MOEDAS - PEBD - LISO - VALIDADE: 01/10/2026 16:18:15. Qtde. Sol.: 1000  Qtde. Disp.: 0</t>
+  </si>
+  <si>
+    <t>00000000000000000000000000811862350000000000</t>
+  </si>
+  <si>
+    <t>DURANTE O PROCESSO, FOI CONSTATADA INSUFICIÊNCIA DE SALDO. PRODUTO: 000000000605002386 - S12-4FUG-050 Conec.c/cabo - VALIDADE: 01/10/2026 16:35:32. Qtde. Sol.: 11  Qtde. Disp.: 0</t>
   </si>
 </sst>
 </file>
@@ -1888,8 +1957,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7522A01F-5450-474A-9B37-7FD19851779C}">
-  <dimension ref="A1:Y62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF11D61D-0367-4316-91D3-C4A55BD5EF3B}">
+  <dimension ref="A1:Y66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -1908,7 +1977,7 @@
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="134.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="133.88671875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="45.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -2157,68 +2226,66 @@
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="W6" s="10" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>38</v>
@@ -2230,66 +2297,68 @@
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>38</v>
@@ -2301,29 +2370,29 @@
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -2360,10 +2429,10 @@
         <v>52</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O9" s="11">
         <v>1</v>
@@ -2372,257 +2441,205 @@
         <v>1</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="U9" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="W9" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y9" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="W9" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
       <c r="O10" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="W10" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="4"/>
       <c r="K11" s="9"/>
       <c r="L11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="O11" s="11">
-        <v>1</v>
+        <v>11122</v>
       </c>
       <c r="P11" s="11">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="9"/>
       <c r="L12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="M12" s="4"/>
       <c r="N12" s="4" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="O12" s="11">
-        <v>1</v>
+        <v>8073</v>
       </c>
       <c r="P12" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="4"/>
@@ -2630,42 +2647,58 @@
       <c r="I13" s="9"/>
       <c r="J13" s="4"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="O13" s="11">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="P13" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
+        <v>276</v>
+      </c>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="4"/>
@@ -2674,57 +2707,57 @@
       <c r="J14" s="4"/>
       <c r="K14" s="9"/>
       <c r="L14" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="O14" s="11">
-        <v>4098</v>
+        <v>224</v>
       </c>
       <c r="P14" s="11">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="4"/>
@@ -2733,57 +2766,57 @@
       <c r="J15" s="4"/>
       <c r="K15" s="9"/>
       <c r="L15" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O15" s="11">
-        <v>6000</v>
+        <v>7040</v>
       </c>
       <c r="P15" s="11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="4"/>
@@ -2792,57 +2825,57 @@
       <c r="J16" s="4"/>
       <c r="K16" s="9"/>
       <c r="L16" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O16" s="11">
-        <v>3000</v>
+        <v>17122</v>
       </c>
       <c r="P16" s="11">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="4"/>
@@ -2851,57 +2884,57 @@
       <c r="J17" s="4"/>
       <c r="K17" s="9"/>
       <c r="L17" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O17" s="11">
-        <v>8073</v>
+        <v>3000</v>
       </c>
       <c r="P17" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V17" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="4"/>
@@ -2910,57 +2943,57 @@
       <c r="J18" s="4"/>
       <c r="K18" s="9"/>
       <c r="L18" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O18" s="11">
-        <v>17122</v>
+        <v>6000</v>
       </c>
       <c r="P18" s="11">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="4"/>
@@ -2969,57 +3002,57 @@
       <c r="J19" s="4"/>
       <c r="K19" s="9"/>
       <c r="L19" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="O19" s="11">
-        <v>7040</v>
+        <v>4098</v>
       </c>
       <c r="P19" s="11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W19" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="4"/>
@@ -3028,11 +3061,11 @@
       <c r="J20" s="4"/>
       <c r="K20" s="9"/>
       <c r="L20" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O20" s="11">
         <v>12</v>
@@ -3041,44 +3074,44 @@
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="4"/>
@@ -3087,57 +3120,59 @@
       <c r="J21" s="4"/>
       <c r="K21" s="9"/>
       <c r="L21" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="O21" s="11">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="P21" s="11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="R21" s="4"/>
       <c r="S21" s="4" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="Y21" s="4" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
+      <c r="A22" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="B22" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="4"/>
@@ -3146,57 +3181,47 @@
       <c r="J22" s="4"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O22" s="11">
-        <v>11122</v>
+        <v>12</v>
       </c>
       <c r="P22" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T22" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="V22" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="W22" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y22" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
+      <c r="A23" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="B23" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>95</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="4"/>
@@ -3205,57 +3230,45 @@
       <c r="J23" s="4"/>
       <c r="K23" s="9"/>
       <c r="L23" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O23" s="11">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="P23" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T23" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="U23" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="V23" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="W23" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="X23" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y23" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="4"/>
@@ -3264,57 +3277,59 @@
       <c r="J24" s="4"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O24" s="11">
-        <v>22121</v>
+        <v>1</v>
       </c>
       <c r="P24" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
+      <c r="A25" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="B25" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="4"/>
@@ -3323,57 +3338,45 @@
       <c r="J25" s="4"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="11">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="P25" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T25" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="V25" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="W25" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="4"/>
@@ -3382,59 +3385,43 @@
       <c r="J26" s="4"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O26" s="11">
-        <v>7048</v>
+        <v>13</v>
       </c>
       <c r="P26" s="11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="R26" s="4"/>
-      <c r="S26" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T26" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="W26" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>224</v>
-      </c>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="4"/>
@@ -3443,25 +3430,23 @@
       <c r="J27" s="4"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O27" s="11">
-        <v>10</v>
+        <v>619</v>
       </c>
       <c r="P27" s="11">
         <v>1</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="R27" s="4"/>
-      <c r="S27" s="4" t="s">
-        <v>294</v>
-      </c>
+      <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
@@ -3470,18 +3455,20 @@
       <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
+      <c r="A28" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="B28" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="4"/>
@@ -3490,59 +3477,45 @@
       <c r="J28" s="4"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O28" s="11">
-        <v>14177</v>
+        <v>4</v>
       </c>
       <c r="P28" s="11">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>296</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="R28" s="4"/>
       <c r="S28" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T28" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="V28" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="W28" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="X28" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y28" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="4"/>
@@ -3551,61 +3524,43 @@
       <c r="J29" s="4"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O29" s="11">
-        <v>13107</v>
+        <v>4</v>
       </c>
       <c r="P29" s="11">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T29" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="U29" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="V29" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="W29" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="X29" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y29" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>117</v>
-      </c>
+      <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="4"/>
@@ -3614,47 +3569,57 @@
       <c r="J30" s="4"/>
       <c r="K30" s="9"/>
       <c r="L30" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="O30" s="11">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="P30" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="R30" s="4"/>
       <c r="S30" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="W30" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y30" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>121</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="4"/>
@@ -3667,40 +3632,52 @@
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="O31" s="11">
-        <v>17</v>
+        <v>7048</v>
       </c>
       <c r="P31" s="11">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="R31" s="4"/>
       <c r="S31" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="T31" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="V31" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="W31" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y31" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>125</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>126</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>127</v>
@@ -3716,20 +3693,20 @@
       </c>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="O32" s="11">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="P32" s="11">
         <v>1</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="R32" s="4"/>
       <c r="S32" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
@@ -3741,189 +3718,153 @@
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="F33" s="9"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="M33" s="4"/>
+      <c r="N33" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="O33" s="11">
-        <v>1</v>
+        <v>14177</v>
       </c>
       <c r="P33" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="R33" s="4"/>
+        <v>310</v>
+      </c>
+      <c r="R33" s="4" t="s">
+        <v>311</v>
+      </c>
       <c r="S33" s="4" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="V33" s="4" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="W33" s="10" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="C34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="O34" s="11">
+        <v>13107</v>
+      </c>
+      <c r="P34" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="S34" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="T34" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="V34" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="W34" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="X34" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y34" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="O34" s="11">
-        <v>1</v>
-      </c>
-      <c r="P34" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="T34" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="V34" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="W34" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="Y34" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="M35" s="4"/>
       <c r="N35" s="4" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="O35" s="11">
         <v>4</v>
@@ -3932,290 +3873,216 @@
         <v>1</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="T35" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="U35" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="V35" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="W35" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="X35" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y35" s="4" t="s">
-        <v>323</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
+      <c r="A36" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="B36" s="4" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="9"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="M36" s="4"/>
       <c r="N36" s="4" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="O36" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P36" s="11">
         <v>1</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="R36" s="4"/>
       <c r="S36" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="T36" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="U36" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="V36" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="W36" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="X36" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="Y36" s="4" t="s">
-        <v>323</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
+      <c r="A37" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="B37" s="4" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>135</v>
-      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="9"/>
       <c r="L37" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="O37" s="11">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="P37" s="11">
         <v>1</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="R37" s="4"/>
       <c r="S37" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="T37" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="U37" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="V37" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="W37" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="X37" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="Y37" s="4" t="s">
-        <v>323</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>135</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="9"/>
       <c r="L38" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="M38" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="O38" s="11">
-        <v>1</v>
+        <v>22121</v>
       </c>
       <c r="P38" s="11">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="R38" s="4"/>
       <c r="S38" s="4" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
       <c r="T38" s="4" t="s">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>341</v>
+        <v>271</v>
       </c>
       <c r="V38" s="4" t="s">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="W38" s="10" t="s">
-        <v>343</v>
+        <v>273</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="Y38" s="4" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O39" s="11">
         <v>1</v>
@@ -4224,144 +4091,144 @@
         <v>1</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="R39" s="4"/>
       <c r="S39" s="4" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="T39" s="4" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="V39" s="4" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="W39" s="10" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="Y39" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="O40" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P40" s="11">
         <v>1</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="R40" s="4"/>
       <c r="S40" s="4" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="U40" s="4" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="W40" s="10" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>231</v>
+        <v>331</v>
       </c>
       <c r="Y40" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="O41" s="11">
         <v>1</v>
@@ -4370,71 +4237,71 @@
         <v>1</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="R41" s="4"/>
       <c r="S41" s="4" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="T41" s="4" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="V41" s="4" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="W41" s="10" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="X41" s="4" t="s">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="Y41" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>170</v>
+        <v>101</v>
       </c>
       <c r="O42" s="11">
         <v>1</v>
@@ -4443,72 +4310,72 @@
         <v>1</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="R42" s="4"/>
       <c r="S42" s="4" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="W42" s="10" t="s">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="Y42" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N43" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L43" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="O43" s="11">
         <v>1</v>
       </c>
@@ -4516,144 +4383,146 @@
         <v>1</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="T43" s="4" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="U43" s="4" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="V43" s="4" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="W43" s="10" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="X43" s="4" t="s">
-        <v>231</v>
+        <v>351</v>
       </c>
       <c r="Y43" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="O44" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P44" s="11">
         <v>1</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="R44" s="4"/>
       <c r="S44" s="4" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="W44" s="10" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="X44" s="4" t="s">
-        <v>385</v>
+        <v>258</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>386</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
+      <c r="A45" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="B45" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="O45" s="11">
         <v>1</v>
@@ -4662,71 +4531,73 @@
         <v>1</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="W45" s="10" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="X45" s="4" t="s">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>224</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
+      <c r="A46" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="B46" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="O46" s="11">
         <v>1</v>
@@ -4735,71 +4606,71 @@
         <v>1</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="R46" s="4"/>
       <c r="S46" s="4" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="W46" s="10" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="X46" s="4" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="Y46" s="4" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="O47" s="11">
         <v>1</v>
@@ -4808,73 +4679,71 @@
         <v>1</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="W47" s="10" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="X47" s="4" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="Y47" s="4" t="s">
-        <v>408</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>177</v>
-      </c>
+      <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="O48" s="11">
         <v>1</v>
@@ -4883,73 +4752,71 @@
         <v>1</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="W48" s="10" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="X48" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Y48" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>179</v>
-      </c>
+      <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="O49" s="11">
         <v>1</v>
@@ -4958,71 +4825,71 @@
         <v>1</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="W49" s="10" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="Y49" s="4" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="O50" s="11">
         <v>1</v>
@@ -5031,144 +4898,144 @@
         <v>1</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="W50" s="10" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="X50" s="4" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="Y50" s="4" t="s">
-        <v>224</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="O51" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" s="11">
         <v>1</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="R51" s="4"/>
       <c r="S51" s="4" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="T51" s="4" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="W51" s="10" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="X51" s="4" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="Y51" s="4" t="s">
-        <v>224</v>
+        <v>373</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="O52" s="11">
         <v>1</v>
@@ -5177,171 +5044,217 @@
         <v>1</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="R52" s="4"/>
       <c r="S52" s="4" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="V52" s="4" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="W52" s="10" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="X52" s="4" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="Y52" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="O53" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P53" s="11">
         <v>1</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="R53" s="4"/>
       <c r="S53" s="4" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="V53" s="4" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="W53" s="10" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="X53" s="4" t="s">
-        <v>448</v>
+        <v>258</v>
       </c>
       <c r="Y53" s="4" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
+        <v>197</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="N54" s="4" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="O54" s="11">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P54" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
+      <c r="S54" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="T54" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="V54" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="W54" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="X54" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y54" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F55" s="9"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="N55" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="O55" s="11">
         <v>1</v>
@@ -5350,339 +5263,719 @@
         <v>1</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="R55" s="4"/>
       <c r="S55" s="4" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="T55" s="4" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="U55" s="4" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="V55" s="4" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="W55" s="10" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="X55" s="4" t="s">
-        <v>456</v>
+        <v>258</v>
       </c>
       <c r="Y55" s="4" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>198</v>
-      </c>
+      <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>182</v>
+      </c>
       <c r="O56" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P56" s="11">
         <v>1</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="R56" s="4"/>
       <c r="S56" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
+        <v>436</v>
+      </c>
+      <c r="T56" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="U56" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="V56" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="W56" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="X56" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y56" s="4" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>201</v>
-      </c>
+      <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
+        <v>217</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="O57" s="11">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P57" s="11">
         <v>1</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="R57" s="4"/>
       <c r="S57" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="10"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
+        <v>442</v>
+      </c>
+      <c r="T57" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="U57" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="V57" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="W57" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="X57" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y57" s="4" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
+        <v>217</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="N58" s="4" t="s">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="O58" s="11">
-        <v>307</v>
+        <v>1</v>
       </c>
       <c r="P58" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
+      <c r="S58" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="T58" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="U58" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="V58" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="W58" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="X58" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y58" s="4" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F59" s="9"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
+        <v>217</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="O59" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="T59" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="U59" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="V59" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="W59" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="R59" s="4" t="s">
+      <c r="X59" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y59" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="O60" s="11">
+        <v>1</v>
+      </c>
+      <c r="P60" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="F60" s="9"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="11">
-        <v>0</v>
-      </c>
-      <c r="P60" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="4" t="s">
+      <c r="R60" s="4"/>
+      <c r="S60" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="R60" s="4" t="s">
+      <c r="T60" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="10"/>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
+      <c r="U60" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="V60" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="W60" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="X60" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="Y60" s="4" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="F61" s="9"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
+        <v>222</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="O61" s="11">
+        <v>1</v>
+      </c>
+      <c r="P61" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="T61" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="U61" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="V61" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="W61" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="X61" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y61" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="O62" s="11">
+        <v>1</v>
+      </c>
+      <c r="P62" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="T62" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="U62" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="V62" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="W62" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="X62" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y62" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="11">
         <v>0</v>
       </c>
-      <c r="P61" s="11">
+      <c r="P63" s="11">
         <v>0</v>
       </c>
-      <c r="Q61" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="R61" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E62" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F62" s="9"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="11">
+      <c r="Q63" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="R63" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="10"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="11">
         <v>0</v>
       </c>
-      <c r="P62" s="11">
+      <c r="P64" s="11">
         <v>0</v>
       </c>
-      <c r="Q62" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="R62" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
+      <c r="Q64" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="R64" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="10"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F65" s="9"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="11">
+        <v>0</v>
+      </c>
+      <c r="P65" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="R65" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="10"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F66" s="9"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="11">
+        <v>0</v>
+      </c>
+      <c r="P66" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="R66" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="10"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
